--- a/plugins/tyroleantape.xlsx
+++ b/plugins/tyroleantape.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usr\pekidocs\python\wallpaper generator\plugins\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimu-tt\Documents\src\WallpaperGenerator_with_plugin\plugins\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A24CCA-4C97-41C6-ADBC-46F8B388AE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21765" windowHeight="11340"/>
+    <workbookView xWindow="4680" yWindow="1008" windowWidth="18384" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
   <si>
     <t>Tape #</t>
     <phoneticPr fontId="1"/>
@@ -131,14 +132,70 @@
   </si>
   <si>
     <t>Save</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Tape</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Parallel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Random</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Spiral</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Vertical</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Horizontal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Diagonal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Color1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Color2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>rrbbgg</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Placer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Incline</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Rotate</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -152,8 +209,16 @@
       <family val="2"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MeiryoKe_UIGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
   </fonts>
-  <fills count="22">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -280,8 +345,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="17">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -477,13 +548,130 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -523,118 +711,169 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="15" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="15" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="21" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="22" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="23" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="25" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="26" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="27" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="9" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -645,12 +884,12 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFDDDDFF"/>
       <color rgb="FFCCFFCC"/>
       <color rgb="FFFFCCFF"/>
       <color rgb="FFCCCCFF"/>
       <color rgb="FFFFF0D0"/>
       <color rgb="FFFFFFDD"/>
-      <color rgb="FFDDDDFF"/>
       <color rgb="FFEDEDFF"/>
       <color rgb="FFCCFFFF"/>
       <color rgb="FF6699FF"/>
@@ -930,20 +1169,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AF19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AT27"/>
+  <sheetFormatPr defaultRowHeight="13.2"/>
   <cols>
-    <col min="1" max="1" width="3.125" customWidth="1"/>
-    <col min="2" max="61" width="2.625" customWidth="1"/>
+    <col min="1" max="1" width="3.109375" customWidth="1"/>
+    <col min="2" max="61" width="2.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:46" ht="13.8" thickBot="1">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:46" ht="13.8" thickBot="1">
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -964,20 +1203,37 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="3"/>
-    </row>
-    <row r="3" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="23"/>
-      <c r="C3" s="13" t="s">
+      <c r="X2" s="1"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
+      <c r="AT2" s="3"/>
+    </row>
+    <row r="3" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B3" s="22"/>
+      <c r="C3" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="46"/>
       <c r="L3" s="7" t="s">
         <v>12</v>
       </c>
@@ -989,19 +1245,35 @@
       <c r="R3" s="8"/>
       <c r="S3" s="8"/>
       <c r="T3" s="9"/>
-      <c r="U3" s="24"/>
-    </row>
-    <row r="4" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="23"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
+      <c r="U3" s="23"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="54" t="s">
+        <v>27</v>
+      </c>
+      <c r="Z3" s="54"/>
+      <c r="AA3" s="54"/>
+      <c r="AB3" s="54"/>
+      <c r="AC3" s="54"/>
+      <c r="AD3" s="54"/>
+      <c r="AE3" s="54"/>
+      <c r="AF3" s="54"/>
+      <c r="AG3" s="54"/>
+      <c r="AH3" s="54"/>
+      <c r="AI3" s="54"/>
+      <c r="AJ3" s="54"/>
+      <c r="AK3" s="54"/>
+      <c r="AL3" s="54"/>
+      <c r="AM3" s="54"/>
+      <c r="AN3" s="54"/>
+      <c r="AO3" s="54"/>
+      <c r="AP3" s="54"/>
+      <c r="AQ3" s="54"/>
+      <c r="AR3" s="54"/>
+      <c r="AS3" s="54"/>
+      <c r="AT3" s="23"/>
+    </row>
+    <row r="4" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B4" s="22"/>
       <c r="L4" s="10" t="s">
         <v>1</v>
       </c>
@@ -1013,210 +1285,337 @@
       <c r="R4" s="11"/>
       <c r="S4" s="11"/>
       <c r="T4" s="12"/>
-      <c r="U4" s="24"/>
-    </row>
-    <row r="5" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="23"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-      <c r="L5" s="13"/>
-      <c r="M5" s="13"/>
-      <c r="N5" s="13"/>
-      <c r="O5" s="13"/>
-      <c r="P5" s="13"/>
-      <c r="Q5" s="13"/>
-      <c r="R5" s="13"/>
-      <c r="S5" s="13"/>
-      <c r="T5" s="13"/>
-      <c r="U5" s="24"/>
-    </row>
-    <row r="6" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="23"/>
-      <c r="C6" s="13" t="s">
+      <c r="U4" s="23"/>
+      <c r="X4" s="22"/>
+      <c r="Y4" s="54">
+        <v>0</v>
+      </c>
+      <c r="Z4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA4" s="8"/>
+      <c r="AB4" s="8"/>
+      <c r="AC4" s="8"/>
+      <c r="AD4" s="8"/>
+      <c r="AE4" s="8"/>
+      <c r="AF4" s="8"/>
+      <c r="AG4" s="8"/>
+      <c r="AH4" s="9"/>
+      <c r="AI4" s="54"/>
+      <c r="AJ4" s="54">
+        <v>5</v>
+      </c>
+      <c r="AK4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL4" s="8"/>
+      <c r="AM4" s="8"/>
+      <c r="AN4" s="8"/>
+      <c r="AO4" s="8"/>
+      <c r="AP4" s="8"/>
+      <c r="AQ4" s="8"/>
+      <c r="AR4" s="8"/>
+      <c r="AS4" s="9"/>
+      <c r="AT4" s="23"/>
+    </row>
+    <row r="5" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B5" s="22"/>
+      <c r="U5" s="23"/>
+      <c r="X5" s="22"/>
+      <c r="Y5" s="54"/>
+      <c r="Z5" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="11"/>
+      <c r="AB5" s="11"/>
+      <c r="AC5" s="11"/>
+      <c r="AD5" s="11"/>
+      <c r="AE5" s="11"/>
+      <c r="AF5" s="11"/>
+      <c r="AG5" s="11"/>
+      <c r="AH5" s="12"/>
+      <c r="AI5" s="54"/>
+      <c r="AJ5" s="54"/>
+      <c r="AK5" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL5" s="11"/>
+      <c r="AM5" s="11"/>
+      <c r="AN5" s="11"/>
+      <c r="AO5" s="11"/>
+      <c r="AP5" s="11"/>
+      <c r="AQ5" s="11"/>
+      <c r="AR5" s="11"/>
+      <c r="AS5" s="12"/>
+      <c r="AT5" s="23"/>
+    </row>
+    <row r="6" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B6" s="22"/>
+      <c r="C6" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="32"/>
-      <c r="I6" s="33" t="s">
+      <c r="F6" s="30"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13" t="s">
+      <c r="K6" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="31"/>
-      <c r="O6" s="32"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="33" t="s">
+      <c r="N6" s="30"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="31"/>
+      <c r="Q6" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="R6" s="13"/>
-      <c r="S6" s="17" t="s">
+      <c r="S6" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="T6" s="18"/>
-      <c r="U6" s="24"/>
-    </row>
-    <row r="7" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="23"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="13"/>
-      <c r="L7" s="13"/>
-      <c r="M7" s="13"/>
-      <c r="N7" s="13"/>
-      <c r="O7" s="13"/>
-      <c r="P7" s="13"/>
-      <c r="Q7" s="13"/>
-      <c r="R7" s="13"/>
-      <c r="S7" s="13"/>
-      <c r="T7" s="13"/>
-      <c r="U7" s="24"/>
-    </row>
-    <row r="8" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="23"/>
-      <c r="C8" s="13" t="s">
+      <c r="T6" s="17"/>
+      <c r="U6" s="23"/>
+      <c r="X6" s="22"/>
+      <c r="Y6" s="54">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA6" s="8"/>
+      <c r="AB6" s="8"/>
+      <c r="AC6" s="8"/>
+      <c r="AD6" s="8"/>
+      <c r="AE6" s="8"/>
+      <c r="AF6" s="8"/>
+      <c r="AG6" s="8"/>
+      <c r="AH6" s="9"/>
+      <c r="AI6" s="54"/>
+      <c r="AJ6" s="54">
         <v>6</v>
       </c>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13">
+      <c r="AK6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL6" s="8"/>
+      <c r="AM6" s="8"/>
+      <c r="AN6" s="8"/>
+      <c r="AO6" s="8"/>
+      <c r="AP6" s="8"/>
+      <c r="AQ6" s="8"/>
+      <c r="AR6" s="8"/>
+      <c r="AS6" s="9"/>
+      <c r="AT6" s="23"/>
+    </row>
+    <row r="7" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B7" s="22"/>
+      <c r="U7" s="23"/>
+      <c r="X7" s="22"/>
+      <c r="Y7" s="54"/>
+      <c r="Z7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="11"/>
+      <c r="AB7" s="11"/>
+      <c r="AC7" s="11"/>
+      <c r="AD7" s="11"/>
+      <c r="AE7" s="11"/>
+      <c r="AF7" s="11"/>
+      <c r="AG7" s="11"/>
+      <c r="AH7" s="12"/>
+      <c r="AI7" s="54"/>
+      <c r="AJ7" s="54"/>
+      <c r="AK7" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL7" s="11"/>
+      <c r="AM7" s="11"/>
+      <c r="AN7" s="11"/>
+      <c r="AO7" s="11"/>
+      <c r="AP7" s="11"/>
+      <c r="AQ7" s="11"/>
+      <c r="AR7" s="11"/>
+      <c r="AS7" s="12"/>
+      <c r="AT7" s="23"/>
+    </row>
+    <row r="8" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B8" s="22"/>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8">
         <v>0</v>
       </c>
-      <c r="G8" s="34"/>
-      <c r="H8" s="35"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="40"/>
-      <c r="N8" s="41"/>
-      <c r="O8" s="42"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="13">
+      <c r="G8" s="33"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="36"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="38"/>
+      <c r="M8" s="39"/>
+      <c r="N8" s="40"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="42"/>
+      <c r="Q8">
         <v>9</v>
       </c>
-      <c r="R8" s="13"/>
-      <c r="S8" s="13"/>
-      <c r="T8" s="13"/>
-      <c r="U8" s="24"/>
-    </row>
-    <row r="9" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="23"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="24"/>
-      <c r="AA9" s="44"/>
-      <c r="AB9" s="44"/>
-      <c r="AC9" s="44"/>
-      <c r="AD9" s="44"/>
-      <c r="AE9" s="44"/>
-      <c r="AF9" s="44"/>
-    </row>
-    <row r="10" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="23"/>
-      <c r="C10" s="13" t="s">
+      <c r="U8" s="23"/>
+      <c r="X8" s="22"/>
+      <c r="Y8" s="54">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+      <c r="AD8" s="8"/>
+      <c r="AE8" s="8"/>
+      <c r="AF8" s="8"/>
+      <c r="AG8" s="8"/>
+      <c r="AH8" s="9"/>
+      <c r="AI8" s="54"/>
+      <c r="AJ8" s="54">
         <v>7</v>
       </c>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="I10" s="33" t="s">
+      <c r="AK8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL8" s="8"/>
+      <c r="AM8" s="8"/>
+      <c r="AN8" s="8"/>
+      <c r="AO8" s="8"/>
+      <c r="AP8" s="8"/>
+      <c r="AQ8" s="8"/>
+      <c r="AR8" s="8"/>
+      <c r="AS8" s="9"/>
+      <c r="AT8" s="23"/>
+    </row>
+    <row r="9" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B9" s="22"/>
+      <c r="U9" s="23"/>
+      <c r="X9" s="22"/>
+      <c r="Y9" s="54"/>
+      <c r="Z9" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="11"/>
+      <c r="AB9" s="11"/>
+      <c r="AC9" s="11"/>
+      <c r="AD9" s="11"/>
+      <c r="AE9" s="11"/>
+      <c r="AF9" s="11"/>
+      <c r="AG9" s="11"/>
+      <c r="AH9" s="12"/>
+      <c r="AI9" s="54"/>
+      <c r="AJ9" s="54"/>
+      <c r="AK9" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL9" s="11"/>
+      <c r="AM9" s="11"/>
+      <c r="AN9" s="11"/>
+      <c r="AO9" s="11"/>
+      <c r="AP9" s="11"/>
+      <c r="AQ9" s="11"/>
+      <c r="AR9" s="11"/>
+      <c r="AS9" s="12"/>
+      <c r="AT9" s="23"/>
+    </row>
+    <row r="10" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B10" s="22"/>
+      <c r="C10" t="s">
+        <v>7</v>
+      </c>
+      <c r="F10" s="30"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13" t="s">
+      <c r="K10" t="s">
         <v>8</v>
       </c>
-      <c r="L10" s="13"/>
-      <c r="M10" s="13"/>
-      <c r="N10" s="31"/>
-      <c r="O10" s="32"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="33" t="s">
+      <c r="N10" s="30"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="31"/>
+      <c r="Q10" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="R10" s="13"/>
-      <c r="S10" s="25" t="s">
+      <c r="S10" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="T10" s="26"/>
-      <c r="U10" s="27"/>
-      <c r="AA10" s="44"/>
-      <c r="AB10" s="44"/>
-      <c r="AC10" s="44"/>
-      <c r="AD10" s="44"/>
-      <c r="AE10" s="44"/>
-      <c r="AF10" s="44"/>
-    </row>
-    <row r="11" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="23"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13"/>
-      <c r="P11" s="13"/>
-      <c r="Q11" s="13"/>
-      <c r="R11" s="13"/>
-      <c r="S11" s="28" t="s">
+      <c r="T10" s="25"/>
+      <c r="U10" s="26"/>
+      <c r="X10" s="22"/>
+      <c r="Y10" s="54">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+      <c r="AD10" s="8"/>
+      <c r="AE10" s="8"/>
+      <c r="AF10" s="8"/>
+      <c r="AG10" s="8"/>
+      <c r="AH10" s="9"/>
+      <c r="AI10" s="54"/>
+      <c r="AJ10" s="54">
+        <v>8</v>
+      </c>
+      <c r="AK10" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL10" s="8"/>
+      <c r="AM10" s="8"/>
+      <c r="AN10" s="8"/>
+      <c r="AO10" s="8"/>
+      <c r="AP10" s="8"/>
+      <c r="AQ10" s="8"/>
+      <c r="AR10" s="8"/>
+      <c r="AS10" s="9"/>
+      <c r="AT10" s="23"/>
+    </row>
+    <row r="11" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B11" s="22"/>
+      <c r="S11" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="T11" s="29"/>
-      <c r="U11" s="30"/>
-      <c r="AA11" s="44"/>
-      <c r="AB11" s="44"/>
-      <c r="AC11" s="44"/>
-      <c r="AD11" s="44"/>
-      <c r="AE11" s="44"/>
-      <c r="AF11" s="44"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
-      <c r="B12" s="50"/>
+      <c r="T11" s="28"/>
+      <c r="U11" s="29"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="54"/>
+      <c r="Z11" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="11"/>
+      <c r="AB11" s="11"/>
+      <c r="AC11" s="11"/>
+      <c r="AD11" s="11"/>
+      <c r="AE11" s="11"/>
+      <c r="AF11" s="11"/>
+      <c r="AG11" s="11"/>
+      <c r="AH11" s="12"/>
+      <c r="AI11" s="54"/>
+      <c r="AJ11" s="54"/>
+      <c r="AK11" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL11" s="11"/>
+      <c r="AM11" s="11"/>
+      <c r="AN11" s="11"/>
+      <c r="AO11" s="11"/>
+      <c r="AP11" s="11"/>
+      <c r="AQ11" s="11"/>
+      <c r="AR11" s="11"/>
+      <c r="AS11" s="12"/>
+      <c r="AT11" s="23"/>
+    </row>
+    <row r="12" spans="1:46">
+      <c r="B12" s="48"/>
       <c r="C12" s="7" t="s">
         <v>11</v>
       </c>
@@ -1232,21 +1631,41 @@
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
       <c r="O12" s="9"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="24"/>
-      <c r="AA12" s="44"/>
-      <c r="AB12" s="44"/>
-      <c r="AC12" s="44"/>
-      <c r="AD12" s="44"/>
-      <c r="AE12" s="44"/>
-      <c r="AF12" s="44"/>
-    </row>
-    <row r="13" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="50"/>
+      <c r="U12" s="23"/>
+      <c r="X12" s="22"/>
+      <c r="Y12" s="54">
+        <v>4</v>
+      </c>
+      <c r="Z12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA12" s="8"/>
+      <c r="AB12" s="8"/>
+      <c r="AC12" s="8"/>
+      <c r="AD12" s="8"/>
+      <c r="AE12" s="8"/>
+      <c r="AF12" s="8"/>
+      <c r="AG12" s="8"/>
+      <c r="AH12" s="9"/>
+      <c r="AI12" s="54"/>
+      <c r="AJ12" s="54">
+        <v>9</v>
+      </c>
+      <c r="AK12" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="AL12" s="8"/>
+      <c r="AM12" s="8"/>
+      <c r="AN12" s="8"/>
+      <c r="AO12" s="8"/>
+      <c r="AP12" s="8"/>
+      <c r="AQ12" s="8"/>
+      <c r="AR12" s="8"/>
+      <c r="AS12" s="9"/>
+      <c r="AT12" s="23"/>
+    </row>
+    <row r="13" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B13" s="48"/>
       <c r="C13" s="10" t="s">
         <v>13</v>
       </c>
@@ -1262,156 +1681,235 @@
       <c r="M13" s="11"/>
       <c r="N13" s="11"/>
       <c r="O13" s="12"/>
-      <c r="P13" s="13"/>
-      <c r="Q13" s="13"/>
-      <c r="R13" s="13"/>
-      <c r="S13" s="13"/>
-      <c r="T13" s="13"/>
-      <c r="U13" s="24"/>
-      <c r="AA13" s="44"/>
-      <c r="AB13" s="44"/>
-      <c r="AC13" s="44"/>
-      <c r="AD13" s="44"/>
-      <c r="AE13" s="44"/>
-      <c r="AF13" s="44"/>
-    </row>
-    <row r="14" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="23"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="13"/>
-      <c r="K14" s="13"/>
-      <c r="L14" s="13"/>
-      <c r="M14" s="13"/>
-      <c r="N14" s="13"/>
-      <c r="O14" s="13"/>
-      <c r="P14" s="13"/>
-      <c r="Q14" s="13"/>
-      <c r="R14" s="13"/>
-      <c r="S14" s="13"/>
-      <c r="T14" s="13"/>
-      <c r="U14" s="24"/>
-    </row>
-    <row r="15" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="23"/>
-      <c r="C15" s="13" t="s">
+      <c r="U13" s="23"/>
+      <c r="X13" s="22"/>
+      <c r="Y13" s="54"/>
+      <c r="Z13" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="11"/>
+      <c r="AB13" s="11"/>
+      <c r="AC13" s="11"/>
+      <c r="AD13" s="11"/>
+      <c r="AE13" s="11"/>
+      <c r="AF13" s="11"/>
+      <c r="AG13" s="11"/>
+      <c r="AH13" s="12"/>
+      <c r="AI13" s="54"/>
+      <c r="AJ13" s="54"/>
+      <c r="AK13" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="AL13" s="11"/>
+      <c r="AM13" s="11"/>
+      <c r="AN13" s="11"/>
+      <c r="AO13" s="11"/>
+      <c r="AP13" s="11"/>
+      <c r="AQ13" s="11"/>
+      <c r="AR13" s="11"/>
+      <c r="AS13" s="12"/>
+      <c r="AT13" s="23"/>
+    </row>
+    <row r="14" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B14" s="22"/>
+      <c r="U14" s="23"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="54"/>
+      <c r="Z14" s="54"/>
+      <c r="AA14" s="54"/>
+      <c r="AB14" s="54"/>
+      <c r="AC14" s="54"/>
+      <c r="AD14" s="54"/>
+      <c r="AE14" s="54"/>
+      <c r="AF14" s="54"/>
+      <c r="AG14" s="54"/>
+      <c r="AH14" s="54"/>
+      <c r="AI14" s="54"/>
+      <c r="AJ14" s="54"/>
+      <c r="AK14" s="54"/>
+      <c r="AL14" s="54"/>
+      <c r="AM14" s="54"/>
+      <c r="AN14" s="54"/>
+      <c r="AO14" s="54"/>
+      <c r="AP14" s="54"/>
+      <c r="AQ14" s="54"/>
+      <c r="AR14" s="54"/>
+      <c r="AS14" s="54"/>
+      <c r="AT14" s="23"/>
+    </row>
+    <row r="15" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B15" s="22"/>
+      <c r="C15" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="48"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="49" t="s">
+      <c r="F15" s="45"/>
+      <c r="G15" s="46"/>
+      <c r="J15" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="K15" s="13" t="s">
+      <c r="K15" t="s">
         <v>16</v>
       </c>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="14" t="s">
+      <c r="N15" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="O15" s="15"/>
-      <c r="P15" s="16"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="24"/>
-    </row>
-    <row r="16" spans="1:32" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="23"/>
-      <c r="C16" s="13" t="s">
+      <c r="O15" s="14"/>
+      <c r="P15" s="15"/>
+      <c r="U15" s="23"/>
+      <c r="X15" s="22"/>
+      <c r="Y15" s="49" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z15" s="54"/>
+      <c r="AA15" s="54"/>
+      <c r="AB15" s="30"/>
+      <c r="AC15" s="31"/>
+      <c r="AD15" s="31"/>
+      <c r="AE15" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF15" s="54"/>
+      <c r="AG15" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="47"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
-      <c r="J16" s="49" t="s">
+      <c r="AH15" s="54"/>
+      <c r="AI15" s="54"/>
+      <c r="AJ15" s="45"/>
+      <c r="AK15" s="46"/>
+      <c r="AL15" s="54"/>
+      <c r="AM15" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN15" s="54"/>
+      <c r="AO15" s="54"/>
+      <c r="AP15" s="45"/>
+      <c r="AQ15" s="46"/>
+      <c r="AR15" s="54"/>
+      <c r="AT15" s="23"/>
+    </row>
+    <row r="16" spans="1:46" ht="13.8" thickBot="1">
+      <c r="B16" s="22"/>
+      <c r="C16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
+      <c r="J16" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="K16" s="13" t="s">
+      <c r="K16" t="s">
         <v>19</v>
       </c>
-      <c r="L16" s="13"/>
-      <c r="M16" s="49" t="s">
+      <c r="M16" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="N16" s="13" t="s">
+      <c r="N16" t="s">
         <v>21</v>
       </c>
-      <c r="O16" s="13"/>
-      <c r="P16" s="13"/>
-      <c r="Q16" s="13"/>
-      <c r="R16" s="13"/>
-      <c r="S16" s="13"/>
-      <c r="T16" s="13"/>
-      <c r="U16" s="24"/>
-    </row>
-    <row r="17" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="23"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
-      <c r="J17" s="13"/>
-      <c r="K17" s="13"/>
-      <c r="L17" s="13"/>
-      <c r="M17" s="13"/>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
-      <c r="P17" s="13"/>
-      <c r="Q17" s="13"/>
-      <c r="R17" s="13"/>
-      <c r="S17" s="13"/>
-      <c r="T17" s="13"/>
-      <c r="U17" s="24"/>
-    </row>
-    <row r="18" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="23"/>
-      <c r="C18" s="45" t="s">
+      <c r="U16" s="23"/>
+      <c r="X16" s="22"/>
+      <c r="Y16" s="54"/>
+      <c r="Z16" s="54"/>
+      <c r="AA16" s="54"/>
+      <c r="AB16" s="54"/>
+      <c r="AC16" s="54"/>
+      <c r="AD16" s="54"/>
+      <c r="AE16" s="54"/>
+      <c r="AF16" s="54"/>
+      <c r="AG16" s="54"/>
+      <c r="AH16" s="54"/>
+      <c r="AI16" s="54"/>
+      <c r="AJ16" s="54"/>
+      <c r="AK16" s="54"/>
+      <c r="AL16" s="54"/>
+      <c r="AM16" s="54"/>
+      <c r="AN16" s="54"/>
+      <c r="AO16" s="54"/>
+      <c r="AP16" s="54"/>
+      <c r="AQ16" s="54"/>
+      <c r="AR16" s="54"/>
+      <c r="AS16" s="54"/>
+      <c r="AT16" s="23"/>
+    </row>
+    <row r="17" spans="2:46" ht="13.8" thickBot="1">
+      <c r="B17" s="22"/>
+      <c r="U17" s="23"/>
+      <c r="X17" s="22"/>
+      <c r="Y17" s="54" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z17" s="30"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="31"/>
+      <c r="AC17" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD17" s="54"/>
+      <c r="AE17" t="s">
+        <v>35</v>
+      </c>
+      <c r="AH17" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI17" s="66"/>
+      <c r="AJ17" s="17"/>
+      <c r="AK17" s="54"/>
+      <c r="AL17" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO17" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="AP17" s="66"/>
+      <c r="AQ17" s="17"/>
+      <c r="AS17" s="54"/>
+      <c r="AT17" s="23"/>
+    </row>
+    <row r="18" spans="2:46" ht="13.8" thickBot="1">
+      <c r="B18" s="22"/>
+      <c r="C18" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="D18" s="46"/>
-      <c r="E18" s="45" t="s">
+      <c r="D18" s="44"/>
+      <c r="E18" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="F18" s="46"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="13"/>
-      <c r="M18" s="13"/>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
-      <c r="P18" s="19" t="s">
+      <c r="F18" s="44"/>
+      <c r="P18" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="Q18" s="20"/>
-      <c r="R18" s="13"/>
-      <c r="S18" s="21" t="s">
+      <c r="Q18" s="19"/>
+      <c r="S18" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="T18" s="22"/>
-      <c r="U18" s="24"/>
-    </row>
-    <row r="19" spans="2:21" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="T18" s="21"/>
+      <c r="U18" s="23"/>
+      <c r="X18" s="22"/>
+      <c r="Y18" s="54"/>
+      <c r="Z18" s="54"/>
+      <c r="AA18" s="54"/>
+      <c r="AB18" s="54"/>
+      <c r="AC18" s="54"/>
+      <c r="AD18" s="54"/>
+      <c r="AE18" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF18" s="54"/>
+      <c r="AG18" s="54"/>
+      <c r="AH18" s="64"/>
+      <c r="AI18" s="65"/>
+      <c r="AK18" s="50"/>
+      <c r="AL18" s="50"/>
+      <c r="AM18" s="54"/>
+      <c r="AN18" s="54"/>
+      <c r="AO18" s="54"/>
+      <c r="AP18" s="54"/>
+      <c r="AQ18" s="54"/>
+      <c r="AR18" s="54"/>
+      <c r="AS18" s="54"/>
+      <c r="AT18" s="23"/>
+    </row>
+    <row r="19" spans="2:46" ht="13.8" thickBot="1">
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -1432,6 +1930,146 @@
       <c r="S19" s="5"/>
       <c r="T19" s="5"/>
       <c r="U19" s="6"/>
+      <c r="X19" s="22"/>
+      <c r="Y19" s="50"/>
+      <c r="Z19" s="50"/>
+      <c r="AA19" s="50"/>
+      <c r="AB19" s="50"/>
+      <c r="AC19" s="50"/>
+      <c r="AD19" s="50"/>
+      <c r="AM19" s="50"/>
+      <c r="AN19" s="50"/>
+      <c r="AO19" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="AP19" s="19"/>
+      <c r="AQ19" s="54"/>
+      <c r="AR19" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS19" s="21"/>
+      <c r="AT19" s="23"/>
+    </row>
+    <row r="20" spans="2:46" ht="13.8" thickBot="1">
+      <c r="X20" s="4"/>
+      <c r="Y20" s="63"/>
+      <c r="Z20" s="63"/>
+      <c r="AA20" s="63"/>
+      <c r="AB20" s="63"/>
+      <c r="AC20" s="63"/>
+      <c r="AD20" s="63"/>
+      <c r="AE20" s="63"/>
+      <c r="AF20" s="63"/>
+      <c r="AG20" s="63"/>
+      <c r="AH20" s="63"/>
+      <c r="AI20" s="63"/>
+      <c r="AJ20" s="63"/>
+      <c r="AK20" s="63"/>
+      <c r="AL20" s="63"/>
+      <c r="AM20" s="63"/>
+      <c r="AN20" s="63"/>
+      <c r="AO20" s="63"/>
+      <c r="AP20" s="63"/>
+      <c r="AQ20" s="5"/>
+      <c r="AR20" s="5"/>
+      <c r="AS20" s="5"/>
+      <c r="AT20" s="6"/>
+    </row>
+    <row r="24" spans="2:46">
+      <c r="Z24" s="67" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA24" s="55"/>
+      <c r="AB24" s="55"/>
+      <c r="AC24" s="56"/>
+      <c r="AD24" s="51" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE24" s="52"/>
+      <c r="AF24" s="52"/>
+      <c r="AG24" s="53"/>
+      <c r="AI24" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ24" s="55"/>
+      <c r="AK24" s="55"/>
+      <c r="AL24" s="55"/>
+      <c r="AM24" s="56"/>
+      <c r="AN24" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="AO24" s="52"/>
+      <c r="AP24" s="52"/>
+      <c r="AQ24" s="52"/>
+      <c r="AR24" s="53"/>
+    </row>
+    <row r="25" spans="2:46">
+      <c r="Z25" s="57"/>
+      <c r="AA25" s="58"/>
+      <c r="AB25" s="58"/>
+      <c r="AC25" s="59"/>
+      <c r="AD25" s="51" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE25" s="52"/>
+      <c r="AF25" s="52"/>
+      <c r="AG25" s="53"/>
+      <c r="AI25" s="57"/>
+      <c r="AJ25" s="58"/>
+      <c r="AK25" s="58"/>
+      <c r="AL25" s="58"/>
+      <c r="AM25" s="59"/>
+      <c r="AN25" s="51" t="s">
+        <v>32</v>
+      </c>
+      <c r="AO25" s="52"/>
+      <c r="AP25" s="52"/>
+      <c r="AQ25" s="52"/>
+      <c r="AR25" s="53"/>
+    </row>
+    <row r="26" spans="2:46">
+      <c r="Z26" s="57"/>
+      <c r="AA26" s="58"/>
+      <c r="AB26" s="58"/>
+      <c r="AC26" s="59"/>
+      <c r="AD26" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE26" s="52"/>
+      <c r="AF26" s="52"/>
+      <c r="AG26" s="53"/>
+      <c r="AI26" s="57"/>
+      <c r="AJ26" s="58"/>
+      <c r="AK26" s="58"/>
+      <c r="AL26" s="58"/>
+      <c r="AM26" s="59"/>
+      <c r="AN26" s="51" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO26" s="52"/>
+      <c r="AP26" s="52"/>
+      <c r="AQ26" s="52"/>
+      <c r="AR26" s="53"/>
+    </row>
+    <row r="27" spans="2:46">
+      <c r="Z27" s="60"/>
+      <c r="AA27" s="61"/>
+      <c r="AB27" s="61"/>
+      <c r="AC27" s="62"/>
+      <c r="AD27" s="51"/>
+      <c r="AE27" s="52"/>
+      <c r="AF27" s="52"/>
+      <c r="AG27" s="53"/>
+      <c r="AI27" s="60"/>
+      <c r="AJ27" s="61"/>
+      <c r="AK27" s="61"/>
+      <c r="AL27" s="61"/>
+      <c r="AM27" s="62"/>
+      <c r="AN27" s="51"/>
+      <c r="AO27" s="52"/>
+      <c r="AP27" s="52"/>
+      <c r="AQ27" s="52"/>
+      <c r="AR27" s="53"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/plugins/tyroleantape.xlsx
+++ b/plugins/tyroleantape.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimu-tt\Documents\src\WallpaperGenerator_with_plugin\plugins\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usr\pekidocs\python\wallpaper generator\plugins\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3A24CCA-4C97-41C6-ADBC-46F8B388AE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="1008" windowWidth="18384" windowHeight="13680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="1005" windowWidth="18390" windowHeight="13680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
   <si>
     <t>Tape #</t>
     <phoneticPr fontId="1"/>
@@ -83,10 +82,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Border</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Spacing</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -183,19 +178,139 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Incline</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Rotate</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tnum</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>preview</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tpsl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tapl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tsel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pal0</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pal9</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>...</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>spsl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sprl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>sadd</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>srmv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ssprvw</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cbdr</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>cspc</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>foutl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fsmpl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fflip</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>fmirr</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Blur</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>coutl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>can</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ok</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Done</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Cancel</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tyld</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tysv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Margin</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Diagonal</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BG Incline</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -218,7 +333,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="23">
+  <fills count="25">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,6 +466,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="28">
     <border>
@@ -671,7 +798,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -874,6 +1001,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -884,6 +1029,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCC99FF"/>
       <color rgb="FFDDDDFF"/>
       <color rgb="FFCCFFCC"/>
       <color rgb="FFFFCCFF"/>
@@ -893,7 +1039,6 @@
       <color rgb="FFEDEDFF"/>
       <color rgb="FFCCFFFF"/>
       <color rgb="FF6699FF"/>
-      <color rgb="FFCC99FF"/>
     </mruColors>
   </colors>
   <extLst>
@@ -905,6 +1050,497 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>41413</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>124239</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>149087</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>107673</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="480391" y="4108174"/>
+          <a:ext cx="3685761" cy="347869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>44726</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>119269</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>152400</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>102704</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="正方形/長方形 2"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="483704" y="4467639"/>
+          <a:ext cx="3685761" cy="347869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>39756</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>106018</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>147430</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>89452</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="478734" y="4818822"/>
+          <a:ext cx="3685761" cy="347869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>26504</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>125897</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>134178</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>109331</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5" name="正方形/長方形 4"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="465482" y="6296440"/>
+          <a:ext cx="3685761" cy="347869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>33131</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>82827</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>140805</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>57980</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="正方形/長方形 5"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="472109" y="5524501"/>
+          <a:ext cx="1101587" cy="704022"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>107673</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>86140</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>149087</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>82826</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="7" name="正方形/長方形 6"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1739347" y="5527814"/>
+          <a:ext cx="2426805" cy="361121"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>102704</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>97735</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>144118</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>94422</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="正方形/長方形 7"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1734378" y="5903844"/>
+          <a:ext cx="2426805" cy="361121"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>31474</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>117614</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>157370</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>106017</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="470452" y="3728831"/>
+          <a:ext cx="3703983" cy="361121"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>117612</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>79514</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>41413</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="正方形/長方形 9"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="357808" y="5156753"/>
+          <a:ext cx="2110409" cy="361121"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1169,20 +1805,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AT27"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AT35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="3.109375" customWidth="1"/>
-    <col min="2" max="61" width="2.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.125" customWidth="1"/>
+    <col min="2" max="61" width="2.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="13.8" thickBot="1">
+    <row r="1" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:46" ht="13.8" thickBot="1">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B2" s="1"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
@@ -1227,7 +1863,7 @@
       <c r="AS2" s="2"/>
       <c r="AT2" s="3"/>
     </row>
-    <row r="3" spans="1:46" ht="13.8" thickBot="1">
+    <row r="3" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="22"/>
       <c r="C3" t="s">
         <v>0</v>
@@ -1248,7 +1884,7 @@
       <c r="U3" s="23"/>
       <c r="X3" s="22"/>
       <c r="Y3" s="54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Z3" s="54"/>
       <c r="AA3" s="54"/>
@@ -1272,7 +1908,7 @@
       <c r="AS3" s="54"/>
       <c r="AT3" s="23"/>
     </row>
-    <row r="4" spans="1:46" ht="13.8" thickBot="1">
+    <row r="4" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="22"/>
       <c r="L4" s="10" t="s">
         <v>1</v>
@@ -1318,7 +1954,7 @@
       <c r="AS4" s="9"/>
       <c r="AT4" s="23"/>
     </row>
-    <row r="5" spans="1:46" ht="13.8" thickBot="1">
+    <row r="5" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B5" s="22"/>
       <c r="U5" s="23"/>
       <c r="X5" s="22"/>
@@ -1349,7 +1985,7 @@
       <c r="AS5" s="12"/>
       <c r="AT5" s="23"/>
     </row>
-    <row r="6" spans="1:46" ht="13.8" thickBot="1">
+    <row r="6" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B6" s="22"/>
       <c r="C6" t="s">
         <v>2</v>
@@ -1406,7 +2042,7 @@
       <c r="AS6" s="9"/>
       <c r="AT6" s="23"/>
     </row>
-    <row r="7" spans="1:46" ht="13.8" thickBot="1">
+    <row r="7" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B7" s="22"/>
       <c r="U7" s="23"/>
       <c r="X7" s="22"/>
@@ -1437,7 +2073,7 @@
       <c r="AS7" s="12"/>
       <c r="AT7" s="23"/>
     </row>
-    <row r="8" spans="1:46" ht="13.8" thickBot="1">
+    <row r="8" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B8" s="22"/>
       <c r="C8" t="s">
         <v>6</v>
@@ -1491,7 +2127,7 @@
       <c r="AS8" s="9"/>
       <c r="AT8" s="23"/>
     </row>
-    <row r="9" spans="1:46" ht="13.8" thickBot="1">
+    <row r="9" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B9" s="22"/>
       <c r="U9" s="23"/>
       <c r="X9" s="22"/>
@@ -1522,7 +2158,7 @@
       <c r="AS9" s="12"/>
       <c r="AT9" s="23"/>
     </row>
-    <row r="10" spans="1:46" ht="13.8" thickBot="1">
+    <row r="10" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B10" s="22"/>
       <c r="C10" t="s">
         <v>7</v>
@@ -1579,7 +2215,7 @@
       <c r="AS10" s="9"/>
       <c r="AT10" s="23"/>
     </row>
-    <row r="11" spans="1:46" ht="13.8" thickBot="1">
+    <row r="11" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B11" s="22"/>
       <c r="S11" s="27" t="s">
         <v>10</v>
@@ -1614,7 +2250,7 @@
       <c r="AS11" s="12"/>
       <c r="AT11" s="23"/>
     </row>
-    <row r="12" spans="1:46">
+    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
       <c r="B12" s="48"/>
       <c r="C12" s="7" t="s">
         <v>11</v>
@@ -1664,7 +2300,7 @@
       <c r="AS12" s="9"/>
       <c r="AT12" s="23"/>
     </row>
-    <row r="13" spans="1:46" ht="13.8" thickBot="1">
+    <row r="13" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B13" s="48"/>
       <c r="C13" s="10" t="s">
         <v>13</v>
@@ -1710,7 +2346,7 @@
       <c r="AS13" s="12"/>
       <c r="AT13" s="23"/>
     </row>
-    <row r="14" spans="1:46" ht="13.8" thickBot="1">
+    <row r="14" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B14" s="22"/>
       <c r="U14" s="23"/>
       <c r="X14" s="22"/>
@@ -1737,28 +2373,28 @@
       <c r="AS14" s="54"/>
       <c r="AT14" s="23"/>
     </row>
-    <row r="15" spans="1:46" ht="13.8" thickBot="1">
+    <row r="15" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="22"/>
       <c r="C15" t="s">
-        <v>14</v>
+        <v>66</v>
       </c>
       <c r="F15" s="45"/>
       <c r="G15" s="46"/>
       <c r="J15" s="47" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K15" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="13" t="s">
         <v>16</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>17</v>
       </c>
       <c r="O15" s="14"/>
       <c r="P15" s="15"/>
       <c r="U15" s="23"/>
       <c r="X15" s="22"/>
       <c r="Y15" s="49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Z15" s="54"/>
       <c r="AA15" s="54"/>
@@ -1770,7 +2406,7 @@
       </c>
       <c r="AF15" s="54"/>
       <c r="AG15" s="54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AH15" s="54"/>
       <c r="AI15" s="54"/>
@@ -1778,7 +2414,7 @@
       <c r="AK15" s="46"/>
       <c r="AL15" s="54"/>
       <c r="AM15" s="54" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AN15" s="54"/>
       <c r="AO15" s="54"/>
@@ -1787,24 +2423,30 @@
       <c r="AR15" s="54"/>
       <c r="AT15" s="23"/>
     </row>
-    <row r="16" spans="1:46" ht="13.8" thickBot="1">
+    <row r="16" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="22"/>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F16" s="45"/>
       <c r="G16" s="46"/>
       <c r="J16" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16" t="s">
         <v>18</v>
       </c>
-      <c r="K16" t="s">
+      <c r="M16" s="47" t="s">
         <v>19</v>
       </c>
-      <c r="M16" s="47" t="s">
+      <c r="N16" t="s">
         <v>20</v>
       </c>
-      <c r="N16" t="s">
-        <v>21</v>
+      <c r="Q16" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="R16" t="s">
+        <v>58</v>
       </c>
       <c r="U16" s="23"/>
       <c r="X16" s="22"/>
@@ -1831,12 +2473,12 @@
       <c r="AS16" s="54"/>
       <c r="AT16" s="23"/>
     </row>
-    <row r="17" spans="2:46" ht="13.8" thickBot="1">
+    <row r="17" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B17" s="22"/>
       <c r="U17" s="23"/>
       <c r="X17" s="22"/>
       <c r="Y17" s="54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="Z17" s="30"/>
       <c r="AA17" s="31"/>
@@ -1846,41 +2488,41 @@
       </c>
       <c r="AD17" s="54"/>
       <c r="AE17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AH17" s="16" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AI17" s="66"/>
       <c r="AJ17" s="17"/>
       <c r="AK17" s="54"/>
       <c r="AL17" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO17" s="16" t="s">
         <v>36</v>
-      </c>
-      <c r="AO17" s="16" t="s">
-        <v>37</v>
       </c>
       <c r="AP17" s="66"/>
       <c r="AQ17" s="17"/>
       <c r="AS17" s="54"/>
       <c r="AT17" s="23"/>
     </row>
-    <row r="18" spans="2:46" ht="13.8" thickBot="1">
+    <row r="18" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B18" s="22"/>
       <c r="C18" s="43" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D18" s="44"/>
       <c r="E18" s="43" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F18" s="44"/>
       <c r="P18" s="18" t="s">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="Q18" s="19"/>
       <c r="S18" s="20" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
@@ -1892,12 +2534,12 @@
       <c r="AC18" s="54"/>
       <c r="AD18" s="54"/>
       <c r="AE18" s="54" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="AF18" s="54"/>
       <c r="AG18" s="54"/>
-      <c r="AH18" s="64"/>
-      <c r="AI18" s="65"/>
+      <c r="AI18" s="64"/>
+      <c r="AJ18" s="65"/>
       <c r="AK18" s="50"/>
       <c r="AL18" s="50"/>
       <c r="AM18" s="54"/>
@@ -1909,7 +2551,7 @@
       <c r="AS18" s="54"/>
       <c r="AT18" s="23"/>
     </row>
-    <row r="19" spans="2:46" ht="13.8" thickBot="1">
+    <row r="19" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
       <c r="D19" s="5"/>
@@ -1940,17 +2582,17 @@
       <c r="AM19" s="50"/>
       <c r="AN19" s="50"/>
       <c r="AO19" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AP19" s="19"/>
       <c r="AQ19" s="54"/>
       <c r="AR19" s="20" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS19" s="21"/>
       <c r="AT19" s="23"/>
     </row>
-    <row r="20" spans="2:46" ht="13.8" thickBot="1">
+    <row r="20" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="X20" s="4"/>
       <c r="Y20" s="63"/>
       <c r="Z20" s="63"/>
@@ -1975,41 +2617,122 @@
       <c r="AS20" s="5"/>
       <c r="AT20" s="6"/>
     </row>
-    <row r="24" spans="2:46">
+    <row r="21" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="E21" s="68" t="s">
+        <v>39</v>
+      </c>
+      <c r="L21" s="69" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
+      <c r="J22" s="73"/>
+      <c r="K22" s="73"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="73"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="73"/>
+      <c r="P22" s="73"/>
+    </row>
+    <row r="23" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="E23" s="70" t="s">
+        <v>41</v>
+      </c>
+      <c r="N23" s="70" t="s">
+        <v>42</v>
+      </c>
+      <c r="S23" s="71" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="24" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="D24" s="73"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
+      <c r="J24" s="73"/>
+      <c r="K24" s="73"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="73"/>
+      <c r="N24" s="73"/>
+      <c r="O24" s="73"/>
+      <c r="P24" s="73"/>
+      <c r="Q24" s="73"/>
+      <c r="R24" s="73"/>
+      <c r="S24" s="73"/>
+      <c r="T24" s="73"/>
+      <c r="U24" s="73"/>
       <c r="Z24" s="67" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AA24" s="55"/>
       <c r="AB24" s="55"/>
       <c r="AC24" s="56"/>
       <c r="AD24" s="51" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE24" s="52"/>
       <c r="AF24" s="52"/>
       <c r="AG24" s="53"/>
       <c r="AI24" s="67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AJ24" s="55"/>
       <c r="AK24" s="55"/>
       <c r="AL24" s="55"/>
       <c r="AM24" s="56"/>
       <c r="AN24" s="51" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AO24" s="52"/>
       <c r="AP24" s="52"/>
       <c r="AQ24" s="52"/>
       <c r="AR24" s="53"/>
     </row>
-    <row r="25" spans="2:46">
+    <row r="25" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="G25" s="71" t="s">
+        <v>44</v>
+      </c>
+      <c r="H25" s="71"/>
+      <c r="I25" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="J25" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="K25" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="L25" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="M25" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="N25" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="O25" s="71" t="s">
+        <v>46</v>
+      </c>
+      <c r="P25" s="71" t="s">
+        <v>45</v>
+      </c>
       <c r="Z25" s="57"/>
       <c r="AA25" s="58"/>
       <c r="AB25" s="58"/>
       <c r="AC25" s="59"/>
       <c r="AD25" s="51" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AE25" s="52"/>
       <c r="AF25" s="52"/>
@@ -2020,20 +2743,37 @@
       <c r="AL25" s="58"/>
       <c r="AM25" s="59"/>
       <c r="AN25" s="51" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AO25" s="52"/>
       <c r="AP25" s="52"/>
       <c r="AQ25" s="52"/>
       <c r="AR25" s="53"/>
     </row>
-    <row r="26" spans="2:46">
+    <row r="26" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="D26" s="73"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73"/>
+      <c r="J26" s="73"/>
+      <c r="K26" s="73"/>
+      <c r="L26" s="73"/>
+      <c r="M26" s="73"/>
+      <c r="N26" s="73"/>
+      <c r="O26" s="73"/>
+      <c r="P26" s="73"/>
+      <c r="Q26" s="73"/>
+      <c r="R26" s="73"/>
+      <c r="S26" s="73"/>
+      <c r="T26" s="73"/>
       <c r="Z26" s="57"/>
       <c r="AA26" s="58"/>
       <c r="AB26" s="58"/>
       <c r="AC26" s="59"/>
       <c r="AD26" s="51" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AE26" s="52"/>
       <c r="AF26" s="52"/>
@@ -2044,14 +2784,26 @@
       <c r="AL26" s="58"/>
       <c r="AM26" s="59"/>
       <c r="AN26" s="51" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AO26" s="52"/>
       <c r="AP26" s="52"/>
       <c r="AQ26" s="52"/>
       <c r="AR26" s="53"/>
     </row>
-    <row r="27" spans="2:46">
+    <row r="27" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="E27" s="70" t="s">
+        <v>47</v>
+      </c>
+      <c r="K27" s="70" t="s">
+        <v>48</v>
+      </c>
+      <c r="P27" s="71" t="s">
+        <v>49</v>
+      </c>
+      <c r="S27" s="71" t="s">
+        <v>50</v>
+      </c>
       <c r="Z27" s="60"/>
       <c r="AA27" s="61"/>
       <c r="AB27" s="61"/>
@@ -2071,9 +2823,160 @@
       <c r="AQ27" s="52"/>
       <c r="AR27" s="53"/>
     </row>
+    <row r="29" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="C29" s="69" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z29" s="67" t="s">
+        <v>67</v>
+      </c>
+      <c r="AA29" s="55"/>
+      <c r="AB29" s="55"/>
+      <c r="AC29" s="56"/>
+      <c r="AD29" s="51" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE29" s="52"/>
+      <c r="AF29" s="52"/>
+      <c r="AG29" s="53"/>
+    </row>
+    <row r="30" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="B30" s="73"/>
+      <c r="C30" s="73"/>
+      <c r="D30" s="73"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
+      <c r="J30" s="73"/>
+      <c r="K30" s="73"/>
+      <c r="L30" s="73"/>
+      <c r="M30" s="73"/>
+      <c r="N30" s="73"/>
+      <c r="O30" s="73"/>
+      <c r="P30" s="73"/>
+      <c r="Q30" s="73"/>
+      <c r="R30" s="73"/>
+      <c r="S30" s="73"/>
+      <c r="T30" s="73"/>
+      <c r="U30" s="73"/>
+      <c r="Z30" s="57"/>
+      <c r="AA30" s="58"/>
+      <c r="AB30" s="58"/>
+      <c r="AC30" s="59"/>
+      <c r="AD30" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE30" s="52"/>
+      <c r="AF30" s="52"/>
+      <c r="AG30" s="53"/>
+    </row>
+    <row r="31" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="F31" s="68" t="s">
+        <v>52</v>
+      </c>
+      <c r="J31" s="72" t="s">
+        <v>54</v>
+      </c>
+      <c r="N31" s="71" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z31" s="57"/>
+      <c r="AA31" s="58"/>
+      <c r="AB31" s="58"/>
+      <c r="AC31" s="59"/>
+      <c r="AD31" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE31" s="52"/>
+      <c r="AF31" s="52"/>
+      <c r="AG31" s="53"/>
+    </row>
+    <row r="32" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="73"/>
+      <c r="M32" s="73"/>
+      <c r="N32" s="73"/>
+      <c r="O32" s="73"/>
+      <c r="P32" s="73"/>
+      <c r="Q32" s="73"/>
+      <c r="R32" s="73"/>
+      <c r="S32" s="73"/>
+      <c r="T32" s="73"/>
+      <c r="Z32" s="60"/>
+      <c r="AA32" s="61"/>
+      <c r="AB32" s="61"/>
+      <c r="AC32" s="62"/>
+      <c r="AD32" s="51"/>
+      <c r="AE32" s="52"/>
+      <c r="AF32" s="52"/>
+      <c r="AG32" s="53"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="F33" s="68" t="s">
+        <v>53</v>
+      </c>
+      <c r="J33" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="M33" s="72" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q33" s="72" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B34" s="73"/>
+      <c r="C34" s="73"/>
+      <c r="D34" s="73"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73"/>
+      <c r="J34" s="73"/>
+      <c r="K34" s="73"/>
+      <c r="L34" s="73"/>
+      <c r="M34" s="73"/>
+      <c r="N34" s="73"/>
+      <c r="O34" s="73"/>
+      <c r="P34" s="73"/>
+      <c r="Q34" s="73"/>
+      <c r="R34" s="73"/>
+      <c r="S34" s="73"/>
+      <c r="T34" s="73"/>
+      <c r="U34" s="73"/>
+      <c r="V34" s="73"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C35" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="P35" s="71" t="s">
+        <v>60</v>
+      </c>
+      <c r="S35" s="71" t="s">
+        <v>61</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/plugins/tyroleantape.xlsx
+++ b/plugins/tyroleantape.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
   <si>
     <t>Tape #</t>
     <phoneticPr fontId="1"/>
@@ -158,18 +158,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>BG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Color1</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Color2</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>rrbbgg</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -294,15 +282,27 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>BG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>Diagonal</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>BG Incline</t>
+    <t>bg_grad</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>placer</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Zoom</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BG1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Incl</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>BG Grad</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -798,7 +798,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -991,12 +991,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="9" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -1019,6 +1013,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2376,7 +2373,7 @@
     <row r="15" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="22"/>
       <c r="C15" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F15" s="45"/>
       <c r="G15" s="46"/>
@@ -2394,7 +2391,7 @@
       <c r="U15" s="23"/>
       <c r="X15" s="22"/>
       <c r="Y15" s="49" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="Z15" s="54"/>
       <c r="AA15" s="54"/>
@@ -2405,22 +2402,22 @@
         <v>3</v>
       </c>
       <c r="AF15" s="54"/>
-      <c r="AG15" s="54" t="s">
+      <c r="AG15" t="s">
+        <v>66</v>
+      </c>
+      <c r="AI15" s="45"/>
+      <c r="AK15" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="AH15" s="54"/>
-      <c r="AI15" s="54"/>
-      <c r="AJ15" s="45"/>
-      <c r="AK15" s="46"/>
       <c r="AL15" s="54"/>
-      <c r="AM15" s="54" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN15" s="54"/>
+      <c r="AN15" s="45"/>
       <c r="AO15" s="54"/>
-      <c r="AP15" s="45"/>
-      <c r="AQ15" s="46"/>
+      <c r="AP15" s="54" t="s">
+        <v>35</v>
+      </c>
+      <c r="AQ15" s="54"/>
       <c r="AR15" s="54"/>
+      <c r="AS15" s="45"/>
       <c r="AT15" s="23"/>
     </row>
     <row r="16" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -2446,7 +2443,7 @@
         <v>17</v>
       </c>
       <c r="R16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="U16" s="23"/>
       <c r="X16" s="22"/>
@@ -2478,33 +2475,35 @@
       <c r="U17" s="23"/>
       <c r="X17" s="22"/>
       <c r="Y17" s="54" t="s">
+        <v>69</v>
+      </c>
+      <c r="AB17" s="30"/>
+      <c r="AC17" s="31"/>
+      <c r="AD17" s="31"/>
+      <c r="AE17" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF17" s="54"/>
+      <c r="AG17" t="s">
+        <v>67</v>
+      </c>
+      <c r="AI17" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="Z17" s="30"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="31"/>
-      <c r="AC17" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD17" s="54"/>
-      <c r="AE17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH17" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="AI17" s="66"/>
-      <c r="AJ17" s="17"/>
-      <c r="AK17" s="54"/>
-      <c r="AL17" s="54" t="s">
-        <v>35</v>
-      </c>
-      <c r="AO17" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="AP17" s="66"/>
-      <c r="AQ17" s="17"/>
-      <c r="AS17" s="54"/>
+      <c r="AJ17" s="64"/>
+      <c r="AK17" s="17"/>
+      <c r="AL17" t="s">
+        <v>67</v>
+      </c>
+      <c r="AN17" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="AO17" s="64"/>
+      <c r="AP17" s="17"/>
+      <c r="AQ17" s="54" t="s">
+        <v>68</v>
+      </c>
+      <c r="AS17" s="45"/>
       <c r="AT17" s="23"/>
     </row>
     <row r="18" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
@@ -2518,11 +2517,11 @@
       </c>
       <c r="F18" s="44"/>
       <c r="P18" s="18" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="Q18" s="19"/>
       <c r="S18" s="20" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="T18" s="21"/>
       <c r="U18" s="23"/>
@@ -2533,13 +2532,11 @@
       <c r="AB18" s="54"/>
       <c r="AC18" s="54"/>
       <c r="AD18" s="54"/>
-      <c r="AE18" s="54" t="s">
-        <v>69</v>
-      </c>
+      <c r="AE18" s="54"/>
       <c r="AF18" s="54"/>
       <c r="AG18" s="54"/>
-      <c r="AI18" s="64"/>
-      <c r="AJ18" s="65"/>
+      <c r="AI18" s="50"/>
+      <c r="AJ18" s="50"/>
       <c r="AK18" s="50"/>
       <c r="AL18" s="50"/>
       <c r="AM18" s="54"/>
@@ -2573,10 +2570,14 @@
       <c r="T19" s="5"/>
       <c r="U19" s="6"/>
       <c r="X19" s="22"/>
-      <c r="Y19" s="50"/>
-      <c r="Z19" s="50"/>
-      <c r="AA19" s="50"/>
-      <c r="AB19" s="50"/>
+      <c r="Y19" s="43" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z19" s="44"/>
+      <c r="AA19" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB19" s="44"/>
       <c r="AC19" s="50"/>
       <c r="AD19" s="50"/>
       <c r="AM19" s="50"/>
@@ -2618,61 +2619,61 @@
       <c r="AT20" s="6"/>
     </row>
     <row r="21" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="E21" s="68" t="s">
+      <c r="E21" s="66" t="s">
+        <v>36</v>
+      </c>
+      <c r="L21" s="67" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="22" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="71"/>
+      <c r="F22" s="71"/>
+      <c r="G22" s="71"/>
+      <c r="H22" s="71"/>
+      <c r="I22" s="71"/>
+      <c r="J22" s="71"/>
+      <c r="K22" s="71"/>
+      <c r="L22" s="71"/>
+      <c r="M22" s="71"/>
+      <c r="N22" s="71"/>
+      <c r="O22" s="71"/>
+      <c r="P22" s="71"/>
+    </row>
+    <row r="23" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="E23" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="N23" s="68" t="s">
         <v>39</v>
       </c>
-      <c r="L21" s="69" t="s">
+      <c r="S23" s="69" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="C22" s="73"/>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
-      <c r="J22" s="73"/>
-      <c r="K22" s="73"/>
-      <c r="L22" s="73"/>
-      <c r="M22" s="73"/>
-      <c r="N22" s="73"/>
-      <c r="O22" s="73"/>
-      <c r="P22" s="73"/>
-    </row>
-    <row r="23" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="E23" s="70" t="s">
-        <v>41</v>
-      </c>
-      <c r="N23" s="70" t="s">
-        <v>42</v>
-      </c>
-      <c r="S23" s="71" t="s">
-        <v>43</v>
-      </c>
-    </row>
     <row r="24" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="D24" s="73"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
-      <c r="J24" s="73"/>
-      <c r="K24" s="73"/>
-      <c r="L24" s="73"/>
-      <c r="M24" s="73"/>
-      <c r="N24" s="73"/>
-      <c r="O24" s="73"/>
-      <c r="P24" s="73"/>
-      <c r="Q24" s="73"/>
-      <c r="R24" s="73"/>
-      <c r="S24" s="73"/>
-      <c r="T24" s="73"/>
-      <c r="U24" s="73"/>
-      <c r="Z24" s="67" t="s">
-        <v>37</v>
+      <c r="D24" s="71"/>
+      <c r="E24" s="71"/>
+      <c r="F24" s="71"/>
+      <c r="G24" s="71"/>
+      <c r="H24" s="71"/>
+      <c r="I24" s="71"/>
+      <c r="J24" s="71"/>
+      <c r="K24" s="71"/>
+      <c r="L24" s="71"/>
+      <c r="M24" s="71"/>
+      <c r="N24" s="71"/>
+      <c r="O24" s="71"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="71"/>
+      <c r="S24" s="71"/>
+      <c r="T24" s="71"/>
+      <c r="U24" s="71"/>
+      <c r="Z24" s="65" t="s">
+        <v>65</v>
       </c>
       <c r="AA24" s="55"/>
       <c r="AB24" s="55"/>
@@ -2683,8 +2684,8 @@
       <c r="AE24" s="52"/>
       <c r="AF24" s="52"/>
       <c r="AG24" s="53"/>
-      <c r="AI24" s="67" t="s">
-        <v>33</v>
+      <c r="AI24" s="65" t="s">
+        <v>64</v>
       </c>
       <c r="AJ24" s="55"/>
       <c r="AK24" s="55"/>
@@ -2699,33 +2700,33 @@
       <c r="AR24" s="53"/>
     </row>
     <row r="25" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="G25" s="71" t="s">
-        <v>44</v>
-      </c>
-      <c r="H25" s="71"/>
-      <c r="I25" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="J25" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="K25" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="L25" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="M25" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="N25" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="O25" s="71" t="s">
-        <v>46</v>
-      </c>
-      <c r="P25" s="71" t="s">
-        <v>45</v>
+      <c r="G25" s="69" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="K25" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="M25" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="N25" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="O25" s="69" t="s">
+        <v>43</v>
+      </c>
+      <c r="P25" s="69" t="s">
+        <v>42</v>
       </c>
       <c r="Z25" s="57"/>
       <c r="AA25" s="58"/>
@@ -2751,23 +2752,23 @@
       <c r="AR25" s="53"/>
     </row>
     <row r="26" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="D26" s="73"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
-      <c r="J26" s="73"/>
-      <c r="K26" s="73"/>
-      <c r="L26" s="73"/>
-      <c r="M26" s="73"/>
-      <c r="N26" s="73"/>
-      <c r="O26" s="73"/>
-      <c r="P26" s="73"/>
-      <c r="Q26" s="73"/>
-      <c r="R26" s="73"/>
-      <c r="S26" s="73"/>
-      <c r="T26" s="73"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="71"/>
+      <c r="F26" s="71"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
+      <c r="I26" s="71"/>
+      <c r="J26" s="71"/>
+      <c r="K26" s="71"/>
+      <c r="L26" s="71"/>
+      <c r="M26" s="71"/>
+      <c r="N26" s="71"/>
+      <c r="O26" s="71"/>
+      <c r="P26" s="71"/>
+      <c r="Q26" s="71"/>
+      <c r="R26" s="71"/>
+      <c r="S26" s="71"/>
+      <c r="T26" s="71"/>
       <c r="Z26" s="57"/>
       <c r="AA26" s="58"/>
       <c r="AB26" s="58"/>
@@ -2792,17 +2793,17 @@
       <c r="AR26" s="53"/>
     </row>
     <row r="27" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="E27" s="70" t="s">
+      <c r="E27" s="68" t="s">
+        <v>44</v>
+      </c>
+      <c r="K27" s="68" t="s">
+        <v>45</v>
+      </c>
+      <c r="P27" s="69" t="s">
+        <v>46</v>
+      </c>
+      <c r="S27" s="69" t="s">
         <v>47</v>
-      </c>
-      <c r="K27" s="70" t="s">
-        <v>48</v>
-      </c>
-      <c r="P27" s="71" t="s">
-        <v>49</v>
-      </c>
-      <c r="S27" s="71" t="s">
-        <v>50</v>
       </c>
       <c r="Z27" s="60"/>
       <c r="AA27" s="61"/>
@@ -2824,153 +2825,153 @@
       <c r="AR27" s="53"/>
     </row>
     <row r="29" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="67" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y29" s="50"/>
+      <c r="Z29" s="72"/>
+      <c r="AA29" s="50"/>
+      <c r="AB29" s="50"/>
+      <c r="AC29" s="50"/>
+      <c r="AD29" s="50"/>
+      <c r="AE29" s="50"/>
+      <c r="AF29" s="50"/>
+      <c r="AG29" s="50"/>
+      <c r="AH29" s="50"/>
+    </row>
+    <row r="30" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="B30" s="71"/>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="71"/>
+      <c r="F30" s="71"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
+      <c r="I30" s="71"/>
+      <c r="J30" s="71"/>
+      <c r="K30" s="71"/>
+      <c r="L30" s="71"/>
+      <c r="M30" s="71"/>
+      <c r="N30" s="71"/>
+      <c r="O30" s="71"/>
+      <c r="P30" s="71"/>
+      <c r="Q30" s="71"/>
+      <c r="R30" s="71"/>
+      <c r="S30" s="71"/>
+      <c r="T30" s="71"/>
+      <c r="U30" s="71"/>
+      <c r="Y30" s="50"/>
+      <c r="Z30" s="50"/>
+      <c r="AA30" s="50"/>
+      <c r="AB30" s="50"/>
+      <c r="AC30" s="50"/>
+      <c r="AD30" s="50"/>
+      <c r="AE30" s="50"/>
+      <c r="AF30" s="50"/>
+      <c r="AG30" s="50"/>
+      <c r="AH30" s="50"/>
+    </row>
+    <row r="31" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="F31" s="66" t="s">
+        <v>49</v>
+      </c>
+      <c r="J31" s="70" t="s">
         <v>51</v>
       </c>
-      <c r="Z29" s="67" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA29" s="55"/>
-      <c r="AB29" s="55"/>
-      <c r="AC29" s="56"/>
-      <c r="AD29" s="51" t="s">
-        <v>31</v>
-      </c>
-      <c r="AE29" s="52"/>
-      <c r="AF29" s="52"/>
-      <c r="AG29" s="53"/>
-    </row>
-    <row r="30" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="B30" s="73"/>
-      <c r="C30" s="73"/>
-      <c r="D30" s="73"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
-      <c r="J30" s="73"/>
-      <c r="K30" s="73"/>
-      <c r="L30" s="73"/>
-      <c r="M30" s="73"/>
-      <c r="N30" s="73"/>
-      <c r="O30" s="73"/>
-      <c r="P30" s="73"/>
-      <c r="Q30" s="73"/>
-      <c r="R30" s="73"/>
-      <c r="S30" s="73"/>
-      <c r="T30" s="73"/>
-      <c r="U30" s="73"/>
-      <c r="Z30" s="57"/>
-      <c r="AA30" s="58"/>
-      <c r="AB30" s="58"/>
-      <c r="AC30" s="59"/>
-      <c r="AD30" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="AE30" s="52"/>
-      <c r="AF30" s="52"/>
-      <c r="AG30" s="53"/>
-    </row>
-    <row r="31" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="F31" s="68" t="s">
+      <c r="N31" s="69" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y31" s="50"/>
+      <c r="Z31" s="50"/>
+      <c r="AA31" s="50"/>
+      <c r="AB31" s="50"/>
+      <c r="AC31" s="50"/>
+      <c r="AD31" s="50"/>
+      <c r="AE31" s="50"/>
+      <c r="AF31" s="50"/>
+      <c r="AG31" s="50"/>
+      <c r="AH31" s="50"/>
+    </row>
+    <row r="32" spans="2:46" x14ac:dyDescent="0.2">
+      <c r="B32" s="71"/>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="71"/>
+      <c r="F32" s="71"/>
+      <c r="G32" s="71"/>
+      <c r="H32" s="71"/>
+      <c r="I32" s="71"/>
+      <c r="J32" s="71"/>
+      <c r="K32" s="71"/>
+      <c r="L32" s="71"/>
+      <c r="M32" s="71"/>
+      <c r="N32" s="71"/>
+      <c r="O32" s="71"/>
+      <c r="P32" s="71"/>
+      <c r="Q32" s="71"/>
+      <c r="R32" s="71"/>
+      <c r="S32" s="71"/>
+      <c r="T32" s="71"/>
+      <c r="Y32" s="50"/>
+      <c r="Z32" s="50"/>
+      <c r="AA32" s="50"/>
+      <c r="AB32" s="50"/>
+      <c r="AC32" s="50"/>
+      <c r="AD32" s="50"/>
+      <c r="AE32" s="50"/>
+      <c r="AF32" s="50"/>
+      <c r="AG32" s="50"/>
+      <c r="AH32" s="50"/>
+    </row>
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="F33" s="66" t="s">
+        <v>50</v>
+      </c>
+      <c r="J33" s="70" t="s">
+        <v>53</v>
+      </c>
+      <c r="M33" s="70" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q33" s="70" t="s">
         <v>52</v>
       </c>
-      <c r="J31" s="72" t="s">
-        <v>54</v>
-      </c>
-      <c r="N31" s="71" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z31" s="57"/>
-      <c r="AA31" s="58"/>
-      <c r="AB31" s="58"/>
-      <c r="AC31" s="59"/>
-      <c r="AD31" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="AE31" s="52"/>
-      <c r="AF31" s="52"/>
-      <c r="AG31" s="53"/>
-    </row>
-    <row r="32" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="B32" s="73"/>
-      <c r="C32" s="73"/>
-      <c r="D32" s="73"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
-      <c r="J32" s="73"/>
-      <c r="K32" s="73"/>
-      <c r="L32" s="73"/>
-      <c r="M32" s="73"/>
-      <c r="N32" s="73"/>
-      <c r="O32" s="73"/>
-      <c r="P32" s="73"/>
-      <c r="Q32" s="73"/>
-      <c r="R32" s="73"/>
-      <c r="S32" s="73"/>
-      <c r="T32" s="73"/>
-      <c r="Z32" s="60"/>
-      <c r="AA32" s="61"/>
-      <c r="AB32" s="61"/>
-      <c r="AC32" s="62"/>
-      <c r="AD32" s="51"/>
-      <c r="AE32" s="52"/>
-      <c r="AF32" s="52"/>
-      <c r="AG32" s="53"/>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="F33" s="68" t="s">
-        <v>53</v>
-      </c>
-      <c r="J33" s="72" t="s">
-        <v>56</v>
-      </c>
-      <c r="M33" s="72" t="s">
+    </row>
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="B34" s="71"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
+      <c r="F34" s="71"/>
+      <c r="G34" s="71"/>
+      <c r="H34" s="71"/>
+      <c r="I34" s="71"/>
+      <c r="J34" s="71"/>
+      <c r="K34" s="71"/>
+      <c r="L34" s="71"/>
+      <c r="M34" s="71"/>
+      <c r="N34" s="71"/>
+      <c r="O34" s="71"/>
+      <c r="P34" s="71"/>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="71"/>
+      <c r="S34" s="71"/>
+      <c r="T34" s="71"/>
+      <c r="U34" s="71"/>
+      <c r="V34" s="71"/>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="C35" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" s="69" t="s">
+        <v>62</v>
+      </c>
+      <c r="P35" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="Q33" s="72" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B34" s="73"/>
-      <c r="C34" s="73"/>
-      <c r="D34" s="73"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="73"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="73"/>
-      <c r="J34" s="73"/>
-      <c r="K34" s="73"/>
-      <c r="L34" s="73"/>
-      <c r="M34" s="73"/>
-      <c r="N34" s="73"/>
-      <c r="O34" s="73"/>
-      <c r="P34" s="73"/>
-      <c r="Q34" s="73"/>
-      <c r="R34" s="73"/>
-      <c r="S34" s="73"/>
-      <c r="T34" s="73"/>
-      <c r="U34" s="73"/>
-      <c r="V34" s="73"/>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C35" s="71" t="s">
-        <v>64</v>
-      </c>
-      <c r="E35" s="71" t="s">
-        <v>65</v>
-      </c>
-      <c r="P35" s="71" t="s">
-        <v>60</v>
-      </c>
-      <c r="S35" s="71" t="s">
-        <v>61</v>
+      <c r="S35" s="69" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/plugins/tyroleantape.xlsx
+++ b/plugins/tyroleantape.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\usr\pekidocs\python\wallpaper generator\plugins\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\kimu-tt\Documents\src\WallpaperGenerator_with_plugin\plugins\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6B977A1-A1CA-45E3-BBED-6C1653550222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="1005" windowWidth="18390" windowHeight="13680"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="83">
   <si>
     <t>Tape #</t>
     <phoneticPr fontId="1"/>
@@ -303,14 +304,66 @@
   </si>
   <si>
     <t>BG Grad</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>pld</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>psv</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Test</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>tst</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>texture</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ftex</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Button</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Checkbox</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Combo(RO)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Slider</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Input</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Text</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Image</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -325,15 +378,22 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="BIZ UDゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <b/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="MeiryoKe_UIGothic"/>
+      <name val="BIZ UDゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="25">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -468,18 +528,48 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="28">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -792,230 +882,298 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="20" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="13" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="14" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="15" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="21" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="22" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="23" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="25" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="26" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="27" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="9" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="23" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="25" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1066,7 +1224,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1120,7 +1284,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2"/>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1174,7 +1344,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="正方形/長方形 3"/>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1228,7 +1404,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1282,7 +1464,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5"/>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000006000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1336,7 +1524,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="正方形/長方形 6"/>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1390,7 +1584,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="正方形/長方形 7"/>
+        <xdr:cNvPr id="8" name="正方形/長方形 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1444,7 +1644,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="正方形/長方形 8"/>
+        <xdr:cNvPr id="9" name="正方形/長方形 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000009000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1498,7 +1704,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="正方形/長方形 9"/>
+        <xdr:cNvPr id="10" name="正方形/長方形 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -1802,1176 +2014,981 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AT35"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AT39"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="3.125" customWidth="1"/>
-    <col min="2" max="61" width="2.625" customWidth="1"/>
+    <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
+    <col min="2" max="61" width="2.6640625" style="1" customWidth="1"/>
+    <col min="62" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:46" ht="14.4" thickBot="1">
+      <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="3"/>
-      <c r="X2" s="1"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2"/>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
-      <c r="AT2" s="3"/>
-    </row>
-    <row r="3" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="22"/>
-      <c r="C3" t="s">
+    <row r="2" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3"/>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="3"/>
+      <c r="T2" s="3"/>
+      <c r="U2" s="4"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="3"/>
+      <c r="Z2" s="3"/>
+      <c r="AA2" s="3"/>
+      <c r="AB2" s="3"/>
+      <c r="AC2" s="3"/>
+      <c r="AD2" s="3"/>
+      <c r="AE2" s="3"/>
+      <c r="AF2" s="3"/>
+      <c r="AG2" s="3"/>
+      <c r="AH2" s="3"/>
+      <c r="AI2" s="3"/>
+      <c r="AJ2" s="3"/>
+      <c r="AK2" s="3"/>
+      <c r="AL2" s="3"/>
+      <c r="AM2" s="3"/>
+      <c r="AN2" s="3"/>
+      <c r="AO2" s="3"/>
+      <c r="AP2" s="3"/>
+      <c r="AQ2" s="3"/>
+      <c r="AR2" s="3"/>
+      <c r="AS2" s="3"/>
+      <c r="AT2" s="4"/>
+    </row>
+    <row r="3" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B3" s="5"/>
+      <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="F3" s="45"/>
-      <c r="G3" s="46"/>
-      <c r="L3" s="7" t="s">
+      <c r="F3" s="75"/>
+      <c r="G3" s="76"/>
+      <c r="J3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="8"/>
-      <c r="O3" s="8"/>
-      <c r="P3" s="8"/>
-      <c r="Q3" s="8"/>
-      <c r="R3" s="8"/>
-      <c r="S3" s="8"/>
-      <c r="T3" s="9"/>
-      <c r="U3" s="23"/>
-      <c r="X3" s="22"/>
-      <c r="Y3" s="54" t="s">
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="10"/>
+      <c r="T3" s="73" t="s">
+        <v>74</v>
+      </c>
+      <c r="U3" s="11"/>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="Z3" s="54"/>
-      <c r="AA3" s="54"/>
-      <c r="AB3" s="54"/>
-      <c r="AC3" s="54"/>
-      <c r="AD3" s="54"/>
-      <c r="AE3" s="54"/>
-      <c r="AF3" s="54"/>
-      <c r="AG3" s="54"/>
-      <c r="AH3" s="54"/>
-      <c r="AI3" s="54"/>
-      <c r="AJ3" s="54"/>
-      <c r="AK3" s="54"/>
-      <c r="AL3" s="54"/>
-      <c r="AM3" s="54"/>
-      <c r="AN3" s="54"/>
-      <c r="AO3" s="54"/>
-      <c r="AP3" s="54"/>
-      <c r="AQ3" s="54"/>
-      <c r="AR3" s="54"/>
-      <c r="AS3" s="54"/>
-      <c r="AT3" s="23"/>
-    </row>
-    <row r="4" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="22"/>
-      <c r="L4" s="10" t="s">
+      <c r="AT3" s="11"/>
+    </row>
+    <row r="4" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B4" s="5"/>
+      <c r="J4" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="12"/>
-      <c r="U4" s="23"/>
-      <c r="X4" s="22"/>
-      <c r="Y4" s="54">
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="14"/>
+      <c r="T4" s="74"/>
+      <c r="U4" s="11"/>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="1">
         <v>0</v>
       </c>
-      <c r="Z4" s="7" t="s">
+      <c r="Z4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
-      <c r="AD4" s="8"/>
-      <c r="AE4" s="8"/>
-      <c r="AF4" s="8"/>
-      <c r="AG4" s="8"/>
-      <c r="AH4" s="9"/>
-      <c r="AI4" s="54"/>
-      <c r="AJ4" s="54">
+      <c r="AA4" s="9"/>
+      <c r="AB4" s="9"/>
+      <c r="AC4" s="9"/>
+      <c r="AD4" s="9"/>
+      <c r="AE4" s="9"/>
+      <c r="AF4" s="9"/>
+      <c r="AG4" s="9"/>
+      <c r="AH4" s="10"/>
+      <c r="AJ4" s="1">
         <v>5</v>
       </c>
-      <c r="AK4" s="7" t="s">
+      <c r="AK4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AL4" s="8"/>
-      <c r="AM4" s="8"/>
-      <c r="AN4" s="8"/>
-      <c r="AO4" s="8"/>
-      <c r="AP4" s="8"/>
-      <c r="AQ4" s="8"/>
-      <c r="AR4" s="8"/>
-      <c r="AS4" s="9"/>
-      <c r="AT4" s="23"/>
-    </row>
-    <row r="5" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="22"/>
-      <c r="U5" s="23"/>
-      <c r="X5" s="22"/>
-      <c r="Y5" s="54"/>
-      <c r="Z5" s="10" t="s">
+      <c r="AL4" s="9"/>
+      <c r="AM4" s="9"/>
+      <c r="AN4" s="9"/>
+      <c r="AO4" s="9"/>
+      <c r="AP4" s="9"/>
+      <c r="AQ4" s="9"/>
+      <c r="AR4" s="9"/>
+      <c r="AS4" s="10"/>
+      <c r="AT4" s="11"/>
+    </row>
+    <row r="5" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B5" s="5"/>
+      <c r="U5" s="11"/>
+      <c r="X5" s="5"/>
+      <c r="Z5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AA5" s="11"/>
-      <c r="AB5" s="11"/>
-      <c r="AC5" s="11"/>
-      <c r="AD5" s="11"/>
-      <c r="AE5" s="11"/>
-      <c r="AF5" s="11"/>
-      <c r="AG5" s="11"/>
-      <c r="AH5" s="12"/>
-      <c r="AI5" s="54"/>
-      <c r="AJ5" s="54"/>
-      <c r="AK5" s="10" t="s">
+      <c r="AA5" s="13"/>
+      <c r="AB5" s="13"/>
+      <c r="AC5" s="13"/>
+      <c r="AD5" s="13"/>
+      <c r="AE5" s="13"/>
+      <c r="AF5" s="13"/>
+      <c r="AG5" s="13"/>
+      <c r="AH5" s="14"/>
+      <c r="AK5" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AL5" s="11"/>
-      <c r="AM5" s="11"/>
-      <c r="AN5" s="11"/>
-      <c r="AO5" s="11"/>
-      <c r="AP5" s="11"/>
-      <c r="AQ5" s="11"/>
-      <c r="AR5" s="11"/>
-      <c r="AS5" s="12"/>
-      <c r="AT5" s="23"/>
-    </row>
-    <row r="6" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="22"/>
-      <c r="C6" t="s">
+      <c r="AL5" s="13"/>
+      <c r="AM5" s="13"/>
+      <c r="AN5" s="13"/>
+      <c r="AO5" s="13"/>
+      <c r="AP5" s="13"/>
+      <c r="AQ5" s="13"/>
+      <c r="AR5" s="13"/>
+      <c r="AS5" s="14"/>
+      <c r="AT5" s="11"/>
+    </row>
+    <row r="6" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B6" s="5"/>
+      <c r="C6" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="32" t="s">
+      <c r="F6" s="15"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
+      <c r="K6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="N6" s="30"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="31"/>
-      <c r="Q6" s="32" t="s">
+      <c r="N6" s="15"/>
+      <c r="O6" s="16"/>
+      <c r="P6" s="16"/>
+      <c r="Q6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="S6" s="16" t="s">
+      <c r="S6" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="T6" s="17"/>
-      <c r="U6" s="23"/>
-      <c r="X6" s="22"/>
-      <c r="Y6" s="54">
+      <c r="T6" s="19"/>
+      <c r="U6" s="11"/>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="1">
         <v>1</v>
       </c>
-      <c r="Z6" s="7" t="s">
+      <c r="Z6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="8"/>
-      <c r="AF6" s="8"/>
-      <c r="AG6" s="8"/>
-      <c r="AH6" s="9"/>
-      <c r="AI6" s="54"/>
-      <c r="AJ6" s="54">
+      <c r="AA6" s="9"/>
+      <c r="AB6" s="9"/>
+      <c r="AC6" s="9"/>
+      <c r="AD6" s="9"/>
+      <c r="AE6" s="9"/>
+      <c r="AF6" s="9"/>
+      <c r="AG6" s="9"/>
+      <c r="AH6" s="10"/>
+      <c r="AJ6" s="1">
         <v>6</v>
       </c>
-      <c r="AK6" s="7" t="s">
+      <c r="AK6" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AL6" s="8"/>
-      <c r="AM6" s="8"/>
-      <c r="AN6" s="8"/>
-      <c r="AO6" s="8"/>
-      <c r="AP6" s="8"/>
-      <c r="AQ6" s="8"/>
-      <c r="AR6" s="8"/>
-      <c r="AS6" s="9"/>
-      <c r="AT6" s="23"/>
-    </row>
-    <row r="7" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="22"/>
-      <c r="U7" s="23"/>
-      <c r="X7" s="22"/>
-      <c r="Y7" s="54"/>
-      <c r="Z7" s="10" t="s">
+      <c r="AL6" s="9"/>
+      <c r="AM6" s="9"/>
+      <c r="AN6" s="9"/>
+      <c r="AO6" s="9"/>
+      <c r="AP6" s="9"/>
+      <c r="AQ6" s="9"/>
+      <c r="AR6" s="9"/>
+      <c r="AS6" s="10"/>
+      <c r="AT6" s="11"/>
+    </row>
+    <row r="7" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B7" s="5"/>
+      <c r="U7" s="11"/>
+      <c r="X7" s="5"/>
+      <c r="Z7" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AA7" s="11"/>
-      <c r="AB7" s="11"/>
-      <c r="AC7" s="11"/>
-      <c r="AD7" s="11"/>
-      <c r="AE7" s="11"/>
-      <c r="AF7" s="11"/>
-      <c r="AG7" s="11"/>
-      <c r="AH7" s="12"/>
-      <c r="AI7" s="54"/>
-      <c r="AJ7" s="54"/>
-      <c r="AK7" s="10" t="s">
+      <c r="AA7" s="13"/>
+      <c r="AB7" s="13"/>
+      <c r="AC7" s="13"/>
+      <c r="AD7" s="13"/>
+      <c r="AE7" s="13"/>
+      <c r="AF7" s="13"/>
+      <c r="AG7" s="13"/>
+      <c r="AH7" s="14"/>
+      <c r="AK7" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AL7" s="11"/>
-      <c r="AM7" s="11"/>
-      <c r="AN7" s="11"/>
-      <c r="AO7" s="11"/>
-      <c r="AP7" s="11"/>
-      <c r="AQ7" s="11"/>
-      <c r="AR7" s="11"/>
-      <c r="AS7" s="12"/>
-      <c r="AT7" s="23"/>
-    </row>
-    <row r="8" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="22"/>
-      <c r="C8" t="s">
+      <c r="AL7" s="13"/>
+      <c r="AM7" s="13"/>
+      <c r="AN7" s="13"/>
+      <c r="AO7" s="13"/>
+      <c r="AP7" s="13"/>
+      <c r="AQ7" s="13"/>
+      <c r="AR7" s="13"/>
+      <c r="AS7" s="14"/>
+      <c r="AT7" s="11"/>
+    </row>
+    <row r="8" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B8" s="5"/>
+      <c r="C8" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>0</v>
       </c>
-      <c r="G8" s="33"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="35"/>
-      <c r="J8" s="36"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="39"/>
-      <c r="N8" s="40"/>
-      <c r="O8" s="41"/>
-      <c r="P8" s="42"/>
-      <c r="Q8">
+      <c r="G8" s="20"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="26"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="28"/>
+      <c r="P8" s="29"/>
+      <c r="Q8" s="1">
         <v>9</v>
       </c>
-      <c r="U8" s="23"/>
-      <c r="X8" s="22"/>
-      <c r="Y8" s="54">
+      <c r="S8" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="T8" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="U8" s="11"/>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="1">
         <v>2</v>
       </c>
-      <c r="Z8" s="7" t="s">
+      <c r="Z8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AA8" s="8"/>
-      <c r="AB8" s="8"/>
-      <c r="AC8" s="8"/>
-      <c r="AD8" s="8"/>
-      <c r="AE8" s="8"/>
-      <c r="AF8" s="8"/>
-      <c r="AG8" s="8"/>
-      <c r="AH8" s="9"/>
-      <c r="AI8" s="54"/>
-      <c r="AJ8" s="54">
+      <c r="AA8" s="9"/>
+      <c r="AB8" s="9"/>
+      <c r="AC8" s="9"/>
+      <c r="AD8" s="9"/>
+      <c r="AE8" s="9"/>
+      <c r="AF8" s="9"/>
+      <c r="AG8" s="9"/>
+      <c r="AH8" s="10"/>
+      <c r="AJ8" s="1">
         <v>7</v>
       </c>
-      <c r="AK8" s="7" t="s">
+      <c r="AK8" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AL8" s="8"/>
-      <c r="AM8" s="8"/>
-      <c r="AN8" s="8"/>
-      <c r="AO8" s="8"/>
-      <c r="AP8" s="8"/>
-      <c r="AQ8" s="8"/>
-      <c r="AR8" s="8"/>
-      <c r="AS8" s="9"/>
-      <c r="AT8" s="23"/>
-    </row>
-    <row r="9" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="22"/>
-      <c r="U9" s="23"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="54"/>
-      <c r="Z9" s="10" t="s">
+      <c r="AL8" s="9"/>
+      <c r="AM8" s="9"/>
+      <c r="AN8" s="9"/>
+      <c r="AO8" s="9"/>
+      <c r="AP8" s="9"/>
+      <c r="AQ8" s="9"/>
+      <c r="AR8" s="9"/>
+      <c r="AS8" s="10"/>
+      <c r="AT8" s="11"/>
+    </row>
+    <row r="9" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B9" s="5"/>
+      <c r="U9" s="11"/>
+      <c r="X9" s="5"/>
+      <c r="Z9" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AA9" s="11"/>
-      <c r="AB9" s="11"/>
-      <c r="AC9" s="11"/>
-      <c r="AD9" s="11"/>
-      <c r="AE9" s="11"/>
-      <c r="AF9" s="11"/>
-      <c r="AG9" s="11"/>
-      <c r="AH9" s="12"/>
-      <c r="AI9" s="54"/>
-      <c r="AJ9" s="54"/>
-      <c r="AK9" s="10" t="s">
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+      <c r="AF9" s="13"/>
+      <c r="AG9" s="13"/>
+      <c r="AH9" s="14"/>
+      <c r="AK9" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AL9" s="11"/>
-      <c r="AM9" s="11"/>
-      <c r="AN9" s="11"/>
-      <c r="AO9" s="11"/>
-      <c r="AP9" s="11"/>
-      <c r="AQ9" s="11"/>
-      <c r="AR9" s="11"/>
-      <c r="AS9" s="12"/>
-      <c r="AT9" s="23"/>
-    </row>
-    <row r="10" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="22"/>
-      <c r="C10" t="s">
+      <c r="AL9" s="13"/>
+      <c r="AM9" s="13"/>
+      <c r="AN9" s="13"/>
+      <c r="AO9" s="13"/>
+      <c r="AP9" s="13"/>
+      <c r="AQ9" s="13"/>
+      <c r="AR9" s="13"/>
+      <c r="AS9" s="14"/>
+      <c r="AT9" s="11"/>
+    </row>
+    <row r="10" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B10" s="5"/>
+      <c r="C10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="32" t="s">
+      <c r="F10" s="15"/>
+      <c r="G10" s="16"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="K10" t="s">
+      <c r="K10" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N10" s="30"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="31"/>
-      <c r="Q10" s="32" t="s">
+      <c r="N10" s="15"/>
+      <c r="O10" s="16"/>
+      <c r="P10" s="16"/>
+      <c r="Q10" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="S10" s="24" t="s">
+      <c r="S10" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="T10" s="25"/>
-      <c r="U10" s="26"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="54">
+      <c r="T10" s="32"/>
+      <c r="U10" s="33"/>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="1">
         <v>3</v>
       </c>
-      <c r="Z10" s="7" t="s">
+      <c r="Z10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AA10" s="8"/>
-      <c r="AB10" s="8"/>
-      <c r="AC10" s="8"/>
-      <c r="AD10" s="8"/>
-      <c r="AE10" s="8"/>
-      <c r="AF10" s="8"/>
-      <c r="AG10" s="8"/>
-      <c r="AH10" s="9"/>
-      <c r="AI10" s="54"/>
-      <c r="AJ10" s="54">
+      <c r="AA10" s="9"/>
+      <c r="AB10" s="9"/>
+      <c r="AC10" s="9"/>
+      <c r="AD10" s="9"/>
+      <c r="AE10" s="9"/>
+      <c r="AF10" s="9"/>
+      <c r="AG10" s="9"/>
+      <c r="AH10" s="10"/>
+      <c r="AJ10" s="1">
         <v>8</v>
       </c>
-      <c r="AK10" s="7" t="s">
+      <c r="AK10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AL10" s="8"/>
-      <c r="AM10" s="8"/>
-      <c r="AN10" s="8"/>
-      <c r="AO10" s="8"/>
-      <c r="AP10" s="8"/>
-      <c r="AQ10" s="8"/>
-      <c r="AR10" s="8"/>
-      <c r="AS10" s="9"/>
-      <c r="AT10" s="23"/>
-    </row>
-    <row r="11" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="22"/>
-      <c r="S11" s="27" t="s">
+      <c r="AL10" s="9"/>
+      <c r="AM10" s="9"/>
+      <c r="AN10" s="9"/>
+      <c r="AO10" s="9"/>
+      <c r="AP10" s="9"/>
+      <c r="AQ10" s="9"/>
+      <c r="AR10" s="9"/>
+      <c r="AS10" s="10"/>
+      <c r="AT10" s="11"/>
+    </row>
+    <row r="11" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B11" s="5"/>
+      <c r="S11" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="T11" s="28"/>
-      <c r="U11" s="29"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="54"/>
-      <c r="Z11" s="10" t="s">
+      <c r="T11" s="35"/>
+      <c r="U11" s="36"/>
+      <c r="X11" s="5"/>
+      <c r="Z11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AA11" s="11"/>
-      <c r="AB11" s="11"/>
-      <c r="AC11" s="11"/>
-      <c r="AD11" s="11"/>
-      <c r="AE11" s="11"/>
-      <c r="AF11" s="11"/>
-      <c r="AG11" s="11"/>
-      <c r="AH11" s="12"/>
-      <c r="AI11" s="54"/>
-      <c r="AJ11" s="54"/>
-      <c r="AK11" s="10" t="s">
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AH11" s="14"/>
+      <c r="AK11" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AL11" s="11"/>
-      <c r="AM11" s="11"/>
-      <c r="AN11" s="11"/>
-      <c r="AO11" s="11"/>
-      <c r="AP11" s="11"/>
-      <c r="AQ11" s="11"/>
-      <c r="AR11" s="11"/>
-      <c r="AS11" s="12"/>
-      <c r="AT11" s="23"/>
-    </row>
-    <row r="12" spans="1:46" x14ac:dyDescent="0.2">
-      <c r="B12" s="48"/>
-      <c r="C12" s="7" t="s">
+      <c r="AL11" s="13"/>
+      <c r="AM11" s="13"/>
+      <c r="AN11" s="13"/>
+      <c r="AO11" s="13"/>
+      <c r="AP11" s="13"/>
+      <c r="AQ11" s="13"/>
+      <c r="AR11" s="13"/>
+      <c r="AS11" s="14"/>
+      <c r="AT11" s="11"/>
+    </row>
+    <row r="12" spans="1:46">
+      <c r="B12" s="37"/>
+      <c r="C12" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="8"/>
-      <c r="O12" s="9"/>
-      <c r="U12" s="23"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="54">
+      <c r="D12" s="9"/>
+      <c r="E12" s="9"/>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9"/>
+      <c r="H12" s="9"/>
+      <c r="I12" s="9"/>
+      <c r="J12" s="9"/>
+      <c r="K12" s="9"/>
+      <c r="L12" s="9"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="10"/>
+      <c r="U12" s="11"/>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="1">
         <v>4</v>
       </c>
-      <c r="Z12" s="7" t="s">
+      <c r="Z12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AA12" s="8"/>
-      <c r="AB12" s="8"/>
-      <c r="AC12" s="8"/>
-      <c r="AD12" s="8"/>
-      <c r="AE12" s="8"/>
-      <c r="AF12" s="8"/>
-      <c r="AG12" s="8"/>
-      <c r="AH12" s="9"/>
-      <c r="AI12" s="54"/>
-      <c r="AJ12" s="54">
+      <c r="AA12" s="9"/>
+      <c r="AB12" s="9"/>
+      <c r="AC12" s="9"/>
+      <c r="AD12" s="9"/>
+      <c r="AE12" s="9"/>
+      <c r="AF12" s="9"/>
+      <c r="AG12" s="9"/>
+      <c r="AH12" s="10"/>
+      <c r="AJ12" s="1">
         <v>9</v>
       </c>
-      <c r="AK12" s="7" t="s">
+      <c r="AK12" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="AL12" s="8"/>
-      <c r="AM12" s="8"/>
-      <c r="AN12" s="8"/>
-      <c r="AO12" s="8"/>
-      <c r="AP12" s="8"/>
-      <c r="AQ12" s="8"/>
-      <c r="AR12" s="8"/>
-      <c r="AS12" s="9"/>
-      <c r="AT12" s="23"/>
-    </row>
-    <row r="13" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="48"/>
-      <c r="C13" s="10" t="s">
+      <c r="AL12" s="9"/>
+      <c r="AM12" s="9"/>
+      <c r="AN12" s="9"/>
+      <c r="AO12" s="9"/>
+      <c r="AP12" s="9"/>
+      <c r="AQ12" s="9"/>
+      <c r="AR12" s="9"/>
+      <c r="AS12" s="10"/>
+      <c r="AT12" s="11"/>
+    </row>
+    <row r="13" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B13" s="37"/>
+      <c r="C13" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
-      <c r="L13" s="11"/>
-      <c r="M13" s="11"/>
-      <c r="N13" s="11"/>
-      <c r="O13" s="12"/>
-      <c r="U13" s="23"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="54"/>
-      <c r="Z13" s="10" t="s">
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+      <c r="N13" s="13"/>
+      <c r="O13" s="14"/>
+      <c r="U13" s="11"/>
+      <c r="X13" s="5"/>
+      <c r="Z13" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AA13" s="11"/>
-      <c r="AB13" s="11"/>
-      <c r="AC13" s="11"/>
-      <c r="AD13" s="11"/>
-      <c r="AE13" s="11"/>
-      <c r="AF13" s="11"/>
-      <c r="AG13" s="11"/>
-      <c r="AH13" s="12"/>
-      <c r="AI13" s="54"/>
-      <c r="AJ13" s="54"/>
-      <c r="AK13" s="10" t="s">
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="13"/>
+      <c r="AD13" s="13"/>
+      <c r="AE13" s="13"/>
+      <c r="AF13" s="13"/>
+      <c r="AG13" s="13"/>
+      <c r="AH13" s="14"/>
+      <c r="AK13" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="AL13" s="11"/>
-      <c r="AM13" s="11"/>
-      <c r="AN13" s="11"/>
-      <c r="AO13" s="11"/>
-      <c r="AP13" s="11"/>
-      <c r="AQ13" s="11"/>
-      <c r="AR13" s="11"/>
-      <c r="AS13" s="12"/>
-      <c r="AT13" s="23"/>
-    </row>
-    <row r="14" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="22"/>
-      <c r="U14" s="23"/>
-      <c r="X14" s="22"/>
-      <c r="Y14" s="54"/>
-      <c r="Z14" s="54"/>
-      <c r="AA14" s="54"/>
-      <c r="AB14" s="54"/>
-      <c r="AC14" s="54"/>
-      <c r="AD14" s="54"/>
-      <c r="AE14" s="54"/>
-      <c r="AF14" s="54"/>
-      <c r="AG14" s="54"/>
-      <c r="AH14" s="54"/>
-      <c r="AI14" s="54"/>
-      <c r="AJ14" s="54"/>
-      <c r="AK14" s="54"/>
-      <c r="AL14" s="54"/>
-      <c r="AM14" s="54"/>
-      <c r="AN14" s="54"/>
-      <c r="AO14" s="54"/>
-      <c r="AP14" s="54"/>
-      <c r="AQ14" s="54"/>
-      <c r="AR14" s="54"/>
-      <c r="AS14" s="54"/>
-      <c r="AT14" s="23"/>
-    </row>
-    <row r="15" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="22"/>
-      <c r="C15" t="s">
+      <c r="AL13" s="13"/>
+      <c r="AM13" s="13"/>
+      <c r="AN13" s="13"/>
+      <c r="AO13" s="13"/>
+      <c r="AP13" s="13"/>
+      <c r="AQ13" s="13"/>
+      <c r="AR13" s="13"/>
+      <c r="AS13" s="14"/>
+      <c r="AT13" s="11"/>
+    </row>
+    <row r="14" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B14" s="5"/>
+      <c r="U14" s="11"/>
+      <c r="X14" s="5"/>
+      <c r="AT14" s="11"/>
+    </row>
+    <row r="15" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B15" s="5"/>
+      <c r="C15" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F15" s="45"/>
-      <c r="G15" s="46"/>
-      <c r="J15" s="47" t="s">
+      <c r="F15" s="6"/>
+      <c r="G15" s="7"/>
+      <c r="J15" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N15" s="13" t="s">
+      <c r="N15" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="O15" s="14"/>
-      <c r="P15" s="15"/>
-      <c r="U15" s="23"/>
-      <c r="X15" s="22"/>
-      <c r="Y15" s="49" t="s">
+      <c r="O15" s="40"/>
+      <c r="P15" s="41"/>
+      <c r="U15" s="11"/>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="42" t="s">
         <v>34</v>
       </c>
-      <c r="Z15" s="54"/>
-      <c r="AA15" s="54"/>
-      <c r="AB15" s="30"/>
-      <c r="AC15" s="31"/>
-      <c r="AD15" s="31"/>
-      <c r="AE15" s="32" t="s">
+      <c r="AB15" s="15"/>
+      <c r="AC15" s="16"/>
+      <c r="AD15" s="16"/>
+      <c r="AE15" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="AF15" s="54"/>
-      <c r="AG15" t="s">
+      <c r="AG15" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="AI15" s="45"/>
-      <c r="AK15" s="54" t="s">
+      <c r="AI15" s="6"/>
+      <c r="AK15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="AL15" s="54"/>
-      <c r="AN15" s="45"/>
-      <c r="AO15" s="54"/>
-      <c r="AP15" s="54" t="s">
+      <c r="AN15" s="6"/>
+      <c r="AP15" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="AQ15" s="54"/>
-      <c r="AR15" s="54"/>
-      <c r="AS15" s="45"/>
-      <c r="AT15" s="23"/>
-    </row>
-    <row r="16" spans="1:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="22"/>
-      <c r="C16" t="s">
+      <c r="AS15" s="6"/>
+      <c r="AT15" s="11"/>
+    </row>
+    <row r="16" spans="1:46" ht="14.4" thickBot="1">
+      <c r="B16" s="5"/>
+      <c r="C16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="46"/>
-      <c r="J16" s="47" t="s">
+      <c r="F16" s="6"/>
+      <c r="G16" s="7"/>
+      <c r="J16" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="K16" t="s">
+      <c r="K16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="M16" s="47" t="s">
+      <c r="M16" s="38" t="s">
         <v>19</v>
       </c>
-      <c r="N16" t="s">
+      <c r="N16" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Q16" s="47" t="s">
+      <c r="Q16" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="R16" t="s">
+      <c r="R16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="U16" s="23"/>
-      <c r="X16" s="22"/>
-      <c r="Y16" s="54"/>
-      <c r="Z16" s="54"/>
-      <c r="AA16" s="54"/>
-      <c r="AB16" s="54"/>
-      <c r="AC16" s="54"/>
-      <c r="AD16" s="54"/>
-      <c r="AE16" s="54"/>
-      <c r="AF16" s="54"/>
-      <c r="AG16" s="54"/>
-      <c r="AH16" s="54"/>
-      <c r="AI16" s="54"/>
-      <c r="AJ16" s="54"/>
-      <c r="AK16" s="54"/>
-      <c r="AL16" s="54"/>
-      <c r="AM16" s="54"/>
-      <c r="AN16" s="54"/>
-      <c r="AO16" s="54"/>
-      <c r="AP16" s="54"/>
-      <c r="AQ16" s="54"/>
-      <c r="AR16" s="54"/>
-      <c r="AS16" s="54"/>
-      <c r="AT16" s="23"/>
-    </row>
-    <row r="17" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="22"/>
-      <c r="U17" s="23"/>
-      <c r="X17" s="22"/>
-      <c r="Y17" s="54" t="s">
+      <c r="U16" s="11"/>
+      <c r="X16" s="5"/>
+      <c r="AT16" s="11"/>
+    </row>
+    <row r="17" spans="2:46" ht="14.4" thickBot="1">
+      <c r="B17" s="5"/>
+      <c r="U17" s="11"/>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="AB17" s="30"/>
-      <c r="AC17" s="31"/>
-      <c r="AD17" s="31"/>
-      <c r="AE17" s="32" t="s">
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="AF17" s="54"/>
-      <c r="AG17" t="s">
+      <c r="AG17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AI17" s="16" t="s">
+      <c r="AI17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="AJ17" s="64"/>
-      <c r="AK17" s="17"/>
-      <c r="AL17" t="s">
+      <c r="AJ17" s="43"/>
+      <c r="AK17" s="19"/>
+      <c r="AL17" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="AN17" s="16" t="s">
+      <c r="AN17" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="AO17" s="64"/>
-      <c r="AP17" s="17"/>
-      <c r="AQ17" s="54" t="s">
+      <c r="AO17" s="43"/>
+      <c r="AP17" s="19"/>
+      <c r="AQ17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="AS17" s="45"/>
-      <c r="AT17" s="23"/>
-    </row>
-    <row r="18" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="22"/>
-      <c r="C18" s="43" t="s">
+      <c r="AS17" s="6"/>
+      <c r="AT17" s="11"/>
+    </row>
+    <row r="18" spans="2:46" ht="14.4" thickBot="1">
+      <c r="B18" s="5"/>
+      <c r="C18" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="D18" s="44"/>
-      <c r="E18" s="43" t="s">
+      <c r="D18" s="45"/>
+      <c r="E18" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="F18" s="44"/>
-      <c r="P18" s="18" t="s">
+      <c r="F18" s="45"/>
+      <c r="M18" s="70" t="s">
+        <v>72</v>
+      </c>
+      <c r="N18" s="71"/>
+      <c r="P18" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="Q18" s="19"/>
-      <c r="S18" s="20" t="s">
+      <c r="Q18" s="47"/>
+      <c r="S18" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="T18" s="21"/>
-      <c r="U18" s="23"/>
-      <c r="X18" s="22"/>
-      <c r="Y18" s="54"/>
-      <c r="Z18" s="54"/>
-      <c r="AA18" s="54"/>
-      <c r="AB18" s="54"/>
-      <c r="AC18" s="54"/>
-      <c r="AD18" s="54"/>
-      <c r="AE18" s="54"/>
-      <c r="AF18" s="54"/>
-      <c r="AG18" s="54"/>
-      <c r="AI18" s="50"/>
-      <c r="AJ18" s="50"/>
-      <c r="AK18" s="50"/>
-      <c r="AL18" s="50"/>
-      <c r="AM18" s="54"/>
-      <c r="AN18" s="54"/>
-      <c r="AO18" s="54"/>
-      <c r="AP18" s="54"/>
-      <c r="AQ18" s="54"/>
-      <c r="AR18" s="54"/>
-      <c r="AS18" s="54"/>
-      <c r="AT18" s="23"/>
-    </row>
-    <row r="19" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="5"/>
-      <c r="K19" s="5"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="5"/>
-      <c r="N19" s="5"/>
-      <c r="O19" s="5"/>
-      <c r="P19" s="5"/>
-      <c r="Q19" s="5"/>
-      <c r="R19" s="5"/>
-      <c r="S19" s="5"/>
-      <c r="T19" s="5"/>
-      <c r="U19" s="6"/>
-      <c r="X19" s="22"/>
-      <c r="Y19" s="43" t="s">
+      <c r="T18" s="49"/>
+      <c r="U18" s="11"/>
+      <c r="X18" s="5"/>
+      <c r="AT18" s="11"/>
+    </row>
+    <row r="19" spans="2:46" ht="14.4" thickBot="1">
+      <c r="B19" s="50"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="51"/>
+      <c r="I19" s="51"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="51"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="51"/>
+      <c r="P19" s="51"/>
+      <c r="Q19" s="51"/>
+      <c r="R19" s="51"/>
+      <c r="S19" s="51"/>
+      <c r="T19" s="51"/>
+      <c r="U19" s="52"/>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="44" t="s">
         <v>24</v>
       </c>
-      <c r="Z19" s="44"/>
-      <c r="AA19" s="43" t="s">
+      <c r="Z19" s="45"/>
+      <c r="AA19" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="AB19" s="44"/>
-      <c r="AC19" s="50"/>
-      <c r="AD19" s="50"/>
-      <c r="AM19" s="50"/>
-      <c r="AN19" s="50"/>
-      <c r="AO19" s="18" t="s">
+      <c r="AB19" s="45"/>
+      <c r="AO19" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="AP19" s="19"/>
-      <c r="AQ19" s="54"/>
-      <c r="AR19" s="20" t="s">
+      <c r="AP19" s="47"/>
+      <c r="AR19" s="48" t="s">
         <v>22</v>
       </c>
-      <c r="AS19" s="21"/>
-      <c r="AT19" s="23"/>
-    </row>
-    <row r="20" spans="2:46" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="X20" s="4"/>
-      <c r="Y20" s="63"/>
-      <c r="Z20" s="63"/>
-      <c r="AA20" s="63"/>
-      <c r="AB20" s="63"/>
-      <c r="AC20" s="63"/>
-      <c r="AD20" s="63"/>
-      <c r="AE20" s="63"/>
-      <c r="AF20" s="63"/>
-      <c r="AG20" s="63"/>
-      <c r="AH20" s="63"/>
-      <c r="AI20" s="63"/>
-      <c r="AJ20" s="63"/>
-      <c r="AK20" s="63"/>
-      <c r="AL20" s="63"/>
-      <c r="AM20" s="63"/>
-      <c r="AN20" s="63"/>
-      <c r="AO20" s="63"/>
-      <c r="AP20" s="63"/>
-      <c r="AQ20" s="5"/>
-      <c r="AR20" s="5"/>
-      <c r="AS20" s="5"/>
-      <c r="AT20" s="6"/>
-    </row>
-    <row r="21" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="E21" s="66" t="s">
+      <c r="AS19" s="49"/>
+      <c r="AT19" s="11"/>
+    </row>
+    <row r="20" spans="2:46" ht="14.4" thickBot="1">
+      <c r="X20" s="50"/>
+      <c r="Y20" s="51"/>
+      <c r="Z20" s="51"/>
+      <c r="AA20" s="51"/>
+      <c r="AB20" s="51"/>
+      <c r="AC20" s="51"/>
+      <c r="AD20" s="51"/>
+      <c r="AE20" s="51"/>
+      <c r="AF20" s="51"/>
+      <c r="AG20" s="51"/>
+      <c r="AH20" s="51"/>
+      <c r="AI20" s="51"/>
+      <c r="AJ20" s="51"/>
+      <c r="AK20" s="51"/>
+      <c r="AL20" s="51"/>
+      <c r="AM20" s="51"/>
+      <c r="AN20" s="51"/>
+      <c r="AO20" s="51"/>
+      <c r="AP20" s="51"/>
+      <c r="AQ20" s="51"/>
+      <c r="AR20" s="51"/>
+      <c r="AS20" s="51"/>
+      <c r="AT20" s="52"/>
+    </row>
+    <row r="21" spans="2:46">
+      <c r="E21" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="L21" s="67" t="s">
+      <c r="I21" s="81"/>
+      <c r="J21" s="80" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="22" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="71"/>
-      <c r="F22" s="71"/>
-      <c r="G22" s="71"/>
-      <c r="H22" s="71"/>
-      <c r="I22" s="71"/>
-      <c r="J22" s="71"/>
-      <c r="K22" s="71"/>
-      <c r="L22" s="71"/>
-      <c r="M22" s="71"/>
-      <c r="N22" s="71"/>
-      <c r="O22" s="71"/>
-      <c r="P22" s="71"/>
-    </row>
-    <row r="23" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="E23" s="68" t="s">
+      <c r="K21" s="80"/>
+      <c r="L21" s="80"/>
+      <c r="M21" s="80"/>
+      <c r="N21" s="80"/>
+      <c r="O21" s="80"/>
+      <c r="P21" s="80"/>
+      <c r="Q21" s="80"/>
+      <c r="S21" s="79" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="2:46">
+      <c r="E23" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="N23" s="68" t="s">
+      <c r="K23" s="72" t="s">
         <v>39</v>
       </c>
-      <c r="S23" s="69" t="s">
+      <c r="S23" s="55" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="D24" s="71"/>
-      <c r="E24" s="71"/>
-      <c r="F24" s="71"/>
-      <c r="G24" s="71"/>
-      <c r="H24" s="71"/>
-      <c r="I24" s="71"/>
-      <c r="J24" s="71"/>
-      <c r="K24" s="71"/>
-      <c r="L24" s="71"/>
-      <c r="M24" s="71"/>
-      <c r="N24" s="71"/>
-      <c r="O24" s="71"/>
-      <c r="P24" s="71"/>
-      <c r="Q24" s="71"/>
-      <c r="R24" s="71"/>
-      <c r="S24" s="71"/>
-      <c r="T24" s="71"/>
-      <c r="U24" s="71"/>
-      <c r="Z24" s="65" t="s">
+    <row r="24" spans="2:46">
+      <c r="Z24" s="56" t="s">
         <v>65</v>
       </c>
-      <c r="AA24" s="55"/>
-      <c r="AB24" s="55"/>
-      <c r="AC24" s="56"/>
-      <c r="AD24" s="51" t="s">
+      <c r="AA24" s="57"/>
+      <c r="AB24" s="57"/>
+      <c r="AC24" s="58"/>
+      <c r="AD24" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="AE24" s="52"/>
-      <c r="AF24" s="52"/>
-      <c r="AG24" s="53"/>
-      <c r="AI24" s="65" t="s">
+      <c r="AE24" s="60"/>
+      <c r="AF24" s="60"/>
+      <c r="AG24" s="61"/>
+      <c r="AI24" s="56" t="s">
         <v>64</v>
       </c>
-      <c r="AJ24" s="55"/>
-      <c r="AK24" s="55"/>
-      <c r="AL24" s="55"/>
-      <c r="AM24" s="56"/>
-      <c r="AN24" s="51" t="s">
+      <c r="AJ24" s="57"/>
+      <c r="AK24" s="57"/>
+      <c r="AL24" s="57"/>
+      <c r="AM24" s="58"/>
+      <c r="AN24" s="59" t="s">
         <v>30</v>
       </c>
-      <c r="AO24" s="52"/>
-      <c r="AP24" s="52"/>
-      <c r="AQ24" s="52"/>
-      <c r="AR24" s="53"/>
-    </row>
-    <row r="25" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="G25" s="69" t="s">
+      <c r="AO24" s="60"/>
+      <c r="AP24" s="60"/>
+      <c r="AQ24" s="60"/>
+      <c r="AR24" s="61"/>
+    </row>
+    <row r="25" spans="2:46">
+      <c r="G25" s="55" t="s">
         <v>41</v>
       </c>
-      <c r="H25" s="69"/>
-      <c r="I25" s="69" t="s">
+      <c r="H25" s="55"/>
+      <c r="I25" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="J25" s="69" t="s">
+      <c r="J25" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="K25" s="69" t="s">
+      <c r="K25" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="L25" s="69" t="s">
+      <c r="L25" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="M25" s="69" t="s">
+      <c r="M25" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="N25" s="69" t="s">
+      <c r="N25" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="O25" s="69" t="s">
+      <c r="O25" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="P25" s="69" t="s">
+      <c r="P25" s="55" t="s">
         <v>42</v>
       </c>
-      <c r="Z25" s="57"/>
-      <c r="AA25" s="58"/>
-      <c r="AB25" s="58"/>
-      <c r="AC25" s="59"/>
-      <c r="AD25" s="51" t="s">
+      <c r="R25" s="55" t="s">
+        <v>70</v>
+      </c>
+      <c r="T25" s="55" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z25" s="62"/>
+      <c r="AA25" s="63"/>
+      <c r="AB25" s="63"/>
+      <c r="AC25" s="64"/>
+      <c r="AD25" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="AE25" s="52"/>
-      <c r="AF25" s="52"/>
-      <c r="AG25" s="53"/>
-      <c r="AI25" s="57"/>
-      <c r="AJ25" s="58"/>
-      <c r="AK25" s="58"/>
-      <c r="AL25" s="58"/>
-      <c r="AM25" s="59"/>
-      <c r="AN25" s="51" t="s">
+      <c r="AE25" s="60"/>
+      <c r="AF25" s="60"/>
+      <c r="AG25" s="61"/>
+      <c r="AI25" s="62"/>
+      <c r="AJ25" s="63"/>
+      <c r="AK25" s="63"/>
+      <c r="AL25" s="63"/>
+      <c r="AM25" s="64"/>
+      <c r="AN25" s="59" t="s">
         <v>31</v>
       </c>
-      <c r="AO25" s="52"/>
-      <c r="AP25" s="52"/>
-      <c r="AQ25" s="52"/>
-      <c r="AR25" s="53"/>
-    </row>
-    <row r="26" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="D26" s="71"/>
-      <c r="E26" s="71"/>
-      <c r="F26" s="71"/>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
-      <c r="I26" s="71"/>
-      <c r="J26" s="71"/>
-      <c r="K26" s="71"/>
-      <c r="L26" s="71"/>
-      <c r="M26" s="71"/>
-      <c r="N26" s="71"/>
-      <c r="O26" s="71"/>
-      <c r="P26" s="71"/>
-      <c r="Q26" s="71"/>
-      <c r="R26" s="71"/>
-      <c r="S26" s="71"/>
-      <c r="T26" s="71"/>
-      <c r="Z26" s="57"/>
-      <c r="AA26" s="58"/>
-      <c r="AB26" s="58"/>
-      <c r="AC26" s="59"/>
-      <c r="AD26" s="51" t="s">
+      <c r="AO25" s="60"/>
+      <c r="AP25" s="60"/>
+      <c r="AQ25" s="60"/>
+      <c r="AR25" s="61"/>
+    </row>
+    <row r="26" spans="2:46">
+      <c r="Z26" s="62"/>
+      <c r="AA26" s="63"/>
+      <c r="AB26" s="63"/>
+      <c r="AC26" s="64"/>
+      <c r="AD26" s="59" t="s">
         <v>29</v>
       </c>
-      <c r="AE26" s="52"/>
-      <c r="AF26" s="52"/>
-      <c r="AG26" s="53"/>
-      <c r="AI26" s="57"/>
-      <c r="AJ26" s="58"/>
-      <c r="AK26" s="58"/>
-      <c r="AL26" s="58"/>
-      <c r="AM26" s="59"/>
-      <c r="AN26" s="51" t="s">
+      <c r="AE26" s="60"/>
+      <c r="AF26" s="60"/>
+      <c r="AG26" s="61"/>
+      <c r="AI26" s="62"/>
+      <c r="AJ26" s="63"/>
+      <c r="AK26" s="63"/>
+      <c r="AL26" s="63"/>
+      <c r="AM26" s="64"/>
+      <c r="AN26" s="59" t="s">
         <v>32</v>
       </c>
-      <c r="AO26" s="52"/>
-      <c r="AP26" s="52"/>
-      <c r="AQ26" s="52"/>
-      <c r="AR26" s="53"/>
-    </row>
-    <row r="27" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="E27" s="68" t="s">
+      <c r="AO26" s="60"/>
+      <c r="AP26" s="60"/>
+      <c r="AQ26" s="60"/>
+      <c r="AR26" s="61"/>
+    </row>
+    <row r="27" spans="2:46">
+      <c r="E27" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="K27" s="68" t="s">
+      <c r="K27" s="72" t="s">
         <v>45</v>
       </c>
-      <c r="P27" s="69" t="s">
+      <c r="P27" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="S27" s="69" t="s">
+      <c r="S27" s="55" t="s">
         <v>47</v>
       </c>
-      <c r="Z27" s="60"/>
-      <c r="AA27" s="61"/>
-      <c r="AB27" s="61"/>
-      <c r="AC27" s="62"/>
-      <c r="AD27" s="51"/>
-      <c r="AE27" s="52"/>
-      <c r="AF27" s="52"/>
-      <c r="AG27" s="53"/>
-      <c r="AI27" s="60"/>
-      <c r="AJ27" s="61"/>
-      <c r="AK27" s="61"/>
-      <c r="AL27" s="61"/>
-      <c r="AM27" s="62"/>
-      <c r="AN27" s="51"/>
-      <c r="AO27" s="52"/>
-      <c r="AP27" s="52"/>
-      <c r="AQ27" s="52"/>
-      <c r="AR27" s="53"/>
-    </row>
-    <row r="29" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="C29" s="67" t="s">
+      <c r="Z27" s="65"/>
+      <c r="AA27" s="66"/>
+      <c r="AB27" s="66"/>
+      <c r="AC27" s="67"/>
+      <c r="AD27" s="59"/>
+      <c r="AE27" s="60"/>
+      <c r="AF27" s="60"/>
+      <c r="AG27" s="61"/>
+      <c r="AI27" s="65"/>
+      <c r="AJ27" s="66"/>
+      <c r="AK27" s="66"/>
+      <c r="AL27" s="66"/>
+      <c r="AM27" s="67"/>
+      <c r="AN27" s="59"/>
+      <c r="AO27" s="60"/>
+      <c r="AP27" s="60"/>
+      <c r="AQ27" s="60"/>
+      <c r="AR27" s="61"/>
+    </row>
+    <row r="29" spans="2:46">
+      <c r="C29" s="80" t="s">
         <v>48</v>
       </c>
-      <c r="Y29" s="50"/>
-      <c r="Z29" s="72"/>
-      <c r="AA29" s="50"/>
-      <c r="AB29" s="50"/>
-      <c r="AC29" s="50"/>
-      <c r="AD29" s="50"/>
-      <c r="AE29" s="50"/>
-      <c r="AF29" s="50"/>
-      <c r="AG29" s="50"/>
-      <c r="AH29" s="50"/>
-    </row>
-    <row r="30" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="B30" s="71"/>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="71"/>
-      <c r="F30" s="71"/>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
-      <c r="I30" s="71"/>
-      <c r="J30" s="71"/>
-      <c r="K30" s="71"/>
-      <c r="L30" s="71"/>
-      <c r="M30" s="71"/>
-      <c r="N30" s="71"/>
-      <c r="O30" s="71"/>
-      <c r="P30" s="71"/>
-      <c r="Q30" s="71"/>
-      <c r="R30" s="71"/>
-      <c r="S30" s="71"/>
-      <c r="T30" s="71"/>
-      <c r="U30" s="71"/>
-      <c r="Y30" s="50"/>
-      <c r="Z30" s="50"/>
-      <c r="AA30" s="50"/>
-      <c r="AB30" s="50"/>
-      <c r="AC30" s="50"/>
-      <c r="AD30" s="50"/>
-      <c r="AE30" s="50"/>
-      <c r="AF30" s="50"/>
-      <c r="AG30" s="50"/>
-      <c r="AH30" s="50"/>
-    </row>
-    <row r="31" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="F31" s="66" t="s">
+      <c r="D29" s="80"/>
+      <c r="E29" s="80"/>
+      <c r="F29" s="80"/>
+      <c r="G29" s="80"/>
+      <c r="H29" s="80"/>
+      <c r="I29" s="80"/>
+      <c r="J29" s="80"/>
+      <c r="K29" s="80"/>
+      <c r="L29" s="80"/>
+      <c r="Z29" s="68"/>
+    </row>
+    <row r="31" spans="2:46">
+      <c r="F31" s="53" t="s">
         <v>49</v>
       </c>
-      <c r="J31" s="70" t="s">
+      <c r="J31" s="69" t="s">
         <v>51</v>
       </c>
-      <c r="N31" s="69" t="s">
+      <c r="N31" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="Y31" s="50"/>
-      <c r="Z31" s="50"/>
-      <c r="AA31" s="50"/>
-      <c r="AB31" s="50"/>
-      <c r="AC31" s="50"/>
-      <c r="AD31" s="50"/>
-      <c r="AE31" s="50"/>
-      <c r="AF31" s="50"/>
-      <c r="AG31" s="50"/>
-      <c r="AH31" s="50"/>
-    </row>
-    <row r="32" spans="2:46" x14ac:dyDescent="0.2">
-      <c r="B32" s="71"/>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="71"/>
-      <c r="F32" s="71"/>
-      <c r="G32" s="71"/>
-      <c r="H32" s="71"/>
-      <c r="I32" s="71"/>
-      <c r="J32" s="71"/>
-      <c r="K32" s="71"/>
-      <c r="L32" s="71"/>
-      <c r="M32" s="71"/>
-      <c r="N32" s="71"/>
-      <c r="O32" s="71"/>
-      <c r="P32" s="71"/>
-      <c r="Q32" s="71"/>
-      <c r="R32" s="71"/>
-      <c r="S32" s="71"/>
-      <c r="T32" s="71"/>
-      <c r="Y32" s="50"/>
-      <c r="Z32" s="50"/>
-      <c r="AA32" s="50"/>
-      <c r="AB32" s="50"/>
-      <c r="AC32" s="50"/>
-      <c r="AD32" s="50"/>
-      <c r="AE32" s="50"/>
-      <c r="AF32" s="50"/>
-      <c r="AG32" s="50"/>
-      <c r="AH32" s="50"/>
-    </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="F33" s="66" t="s">
+    </row>
+    <row r="33" spans="3:21">
+      <c r="F33" s="53" t="s">
         <v>50</v>
       </c>
-      <c r="J33" s="70" t="s">
+      <c r="J33" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="M33" s="70" t="s">
+      <c r="M33" s="69" t="s">
         <v>54</v>
       </c>
-      <c r="Q33" s="70" t="s">
+      <c r="Q33" s="69" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="B34" s="71"/>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
-      <c r="F34" s="71"/>
-      <c r="G34" s="71"/>
-      <c r="H34" s="71"/>
-      <c r="I34" s="71"/>
-      <c r="J34" s="71"/>
-      <c r="K34" s="71"/>
-      <c r="L34" s="71"/>
-      <c r="M34" s="71"/>
-      <c r="N34" s="71"/>
-      <c r="O34" s="71"/>
-      <c r="P34" s="71"/>
-      <c r="Q34" s="71"/>
-      <c r="R34" s="71"/>
-      <c r="S34" s="71"/>
-      <c r="T34" s="71"/>
-      <c r="U34" s="71"/>
-      <c r="V34" s="71"/>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
-      <c r="C35" s="69" t="s">
+    <row r="35" spans="3:21">
+      <c r="C35" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="E35" s="69" t="s">
+      <c r="E35" s="55" t="s">
         <v>62</v>
       </c>
-      <c r="P35" s="69" t="s">
+      <c r="N35" s="55" t="s">
+        <v>73</v>
+      </c>
+      <c r="P35" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="S35" s="69" t="s">
+      <c r="S35" s="55" t="s">
         <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="3:21">
+      <c r="C38" s="55"/>
+      <c r="D38" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I38" s="72"/>
+      <c r="J38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="O38" s="79"/>
+      <c r="P38" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T38" s="54"/>
+      <c r="U38" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="39" spans="3:21">
+      <c r="C39" s="78"/>
+      <c r="D39" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="I39" s="53"/>
+      <c r="J39" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="O39" s="77"/>
+      <c r="P39" s="1" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
